--- a/VerveStacks_ZAF/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,29 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C50D758C-342C-4305-9A17-67DF9802A849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9FABAEA-AAC2-49F9-B729-97F9701B6617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
-    <sheet name="hydro" sheetId="6" r:id="rId2"/>
-    <sheet name="ELC_Storage" sheetId="9" r:id="rId3"/>
-    <sheet name="EV Battery" sheetId="10" r:id="rId4"/>
-    <sheet name="H2 prod" sheetId="11" r:id="rId5"/>
-    <sheet name="solar" sheetId="12" r:id="rId6"/>
-    <sheet name="wind" sheetId="13" r:id="rId7"/>
-    <sheet name="conventional" sheetId="14" r:id="rId8"/>
+    <sheet name="ELC_Storage" sheetId="9" r:id="rId2"/>
+    <sheet name="EV Battery" sheetId="10" r:id="rId3"/>
+    <sheet name="H2 prod" sheetId="11" r:id="rId4"/>
+    <sheet name="solar" sheetId="12" r:id="rId5"/>
+    <sheet name="wind" sheetId="13" r:id="rId6"/>
+    <sheet name="conventional" sheetId="14" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="FuelList">[1]ELC_Lists!$K$4:$K$113</definedName>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="520">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -619,330 +618,303 @@
     <t>wnid offshore potential</t>
   </si>
   <si>
+    <t>ELC_BatIn</t>
+  </si>
+  <si>
     <t>~fi_process</t>
   </si>
   <si>
+    <t>set</t>
+  </si>
+  <si>
     <t>process</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
+    <t>capacity_unit</t>
+  </si>
+  <si>
+    <t>activity_unit</t>
+  </si>
+  <si>
     <t>timeslicelevel</t>
   </si>
   <si>
-    <t>EN_Hydro_ZAF-1</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - South Africa - Step 1</t>
-  </si>
-  <si>
-    <t>PJ</t>
-  </si>
-  <si>
-    <t>EN_Hydro_ZAF-2</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - South Africa - Step 2</t>
-  </si>
-  <si>
-    <t>EN_Hydro_ZAF-3</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - South Africa - Step 3</t>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>ele</t>
+  </si>
+  <si>
+    <t>e_spv_001</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 1</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>e_spv_002</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 2</t>
+  </si>
+  <si>
+    <t>e_spv_003</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 3</t>
+  </si>
+  <si>
+    <t>e_spv_004</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 4</t>
+  </si>
+  <si>
+    <t>e_spv_005</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 5</t>
+  </si>
+  <si>
+    <t>e_spv_006</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 6</t>
+  </si>
+  <si>
+    <t>e_spv_007</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 7</t>
+  </si>
+  <si>
+    <t>e_spv_008</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 8</t>
+  </si>
+  <si>
+    <t>e_spv_009</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 9</t>
+  </si>
+  <si>
+    <t>e_spv_010</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 10</t>
+  </si>
+  <si>
+    <t>e_spv_011</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 11</t>
+  </si>
+  <si>
+    <t>e_spv_012</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 12</t>
+  </si>
+  <si>
+    <t>e_spv_013</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 13</t>
+  </si>
+  <si>
+    <t>e_spv_014</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 14</t>
+  </si>
+  <si>
+    <t>e_spv_015</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 15</t>
+  </si>
+  <si>
+    <t>e_spv_016</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 16</t>
+  </si>
+  <si>
+    <t>e_spv_017</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 17</t>
+  </si>
+  <si>
+    <t>e_spv_018</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 18</t>
+  </si>
+  <si>
+    <t>e_spv_019</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 19</t>
+  </si>
+  <si>
+    <t>e_spv_020</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 20</t>
+  </si>
+  <si>
+    <t>e_spv_021</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 21</t>
+  </si>
+  <si>
+    <t>e_spv_022</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 22</t>
+  </si>
+  <si>
+    <t>e_spv_023</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 23</t>
+  </si>
+  <si>
+    <t>e_spv_024</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 24</t>
+  </si>
+  <si>
+    <t>e_spv_025</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 25</t>
+  </si>
+  <si>
+    <t>e_spv_026</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 26</t>
+  </si>
+  <si>
+    <t>e_spv_027</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 27</t>
+  </si>
+  <si>
+    <t>e_spv_028</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 28</t>
+  </si>
+  <si>
+    <t>e_spv_029</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 29</t>
+  </si>
+  <si>
+    <t>e_spv_030</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 30</t>
+  </si>
+  <si>
+    <t>e_spv_031</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 31</t>
+  </si>
+  <si>
+    <t>e_spv_032</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 32</t>
+  </si>
+  <si>
+    <t>e_spv_033</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 33</t>
+  </si>
+  <si>
+    <t>e_spv_034</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 34</t>
+  </si>
+  <si>
+    <t>e_spv_035</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 35</t>
+  </si>
+  <si>
+    <t>e_spv_036</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 36</t>
+  </si>
+  <si>
+    <t>e_spv_037</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 37</t>
+  </si>
+  <si>
+    <t>e_spv_038</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 38</t>
+  </si>
+  <si>
+    <t>e_spv_039</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 39</t>
+  </si>
+  <si>
+    <t>e_spv_040</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 40</t>
+  </si>
+  <si>
+    <t>e_spv_041</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 41</t>
+  </si>
+  <si>
+    <t>e_spv_042</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 42</t>
+  </si>
+  <si>
+    <t>e_spv_043</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 43</t>
   </si>
   <si>
     <t>~fi_t</t>
   </si>
   <si>
-    <t>CAP_BND</t>
-  </si>
-  <si>
-    <t>INVCOST~USD21_alt</t>
-  </si>
-  <si>
-    <t>AF~FX</t>
-  </si>
-  <si>
-    <t>set</t>
-  </si>
-  <si>
-    <t>capacity_unit</t>
-  </si>
-  <si>
-    <t>activity_unit</t>
-  </si>
-  <si>
-    <t>vintage</t>
-  </si>
-  <si>
-    <t>ele</t>
-  </si>
-  <si>
-    <t>e_spv_001</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 1</t>
-  </si>
-  <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>e_spv_002</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 2</t>
-  </si>
-  <si>
-    <t>e_spv_003</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 3</t>
-  </si>
-  <si>
-    <t>e_spv_004</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 4</t>
-  </si>
-  <si>
-    <t>e_spv_005</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 5</t>
-  </si>
-  <si>
-    <t>e_spv_006</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 6</t>
-  </si>
-  <si>
-    <t>e_spv_007</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 7</t>
-  </si>
-  <si>
-    <t>e_spv_008</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 8</t>
-  </si>
-  <si>
-    <t>e_spv_009</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 9</t>
-  </si>
-  <si>
-    <t>e_spv_010</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 10</t>
-  </si>
-  <si>
-    <t>e_spv_011</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 11</t>
-  </si>
-  <si>
-    <t>e_spv_012</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 12</t>
-  </si>
-  <si>
-    <t>e_spv_013</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 13</t>
-  </si>
-  <si>
-    <t>e_spv_014</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 14</t>
-  </si>
-  <si>
-    <t>e_spv_015</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 15</t>
-  </si>
-  <si>
-    <t>e_spv_016</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 16</t>
-  </si>
-  <si>
-    <t>e_spv_017</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 17</t>
-  </si>
-  <si>
-    <t>e_spv_018</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 18</t>
-  </si>
-  <si>
-    <t>e_spv_019</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 19</t>
-  </si>
-  <si>
-    <t>e_spv_020</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 20</t>
-  </si>
-  <si>
-    <t>e_spv_021</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 21</t>
-  </si>
-  <si>
-    <t>e_spv_022</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 22</t>
-  </si>
-  <si>
-    <t>e_spv_023</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 23</t>
-  </si>
-  <si>
-    <t>e_spv_024</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 24</t>
-  </si>
-  <si>
-    <t>e_spv_025</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 25</t>
-  </si>
-  <si>
-    <t>e_spv_026</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 26</t>
-  </si>
-  <si>
-    <t>e_spv_027</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 27</t>
-  </si>
-  <si>
-    <t>e_spv_028</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 28</t>
-  </si>
-  <si>
-    <t>e_spv_029</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 29</t>
-  </si>
-  <si>
-    <t>e_spv_030</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 30</t>
-  </si>
-  <si>
-    <t>e_spv_031</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 31</t>
-  </si>
-  <si>
-    <t>e_spv_032</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 32</t>
-  </si>
-  <si>
-    <t>e_spv_033</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 33</t>
-  </si>
-  <si>
-    <t>e_spv_034</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 34</t>
-  </si>
-  <si>
-    <t>e_spv_035</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 35</t>
-  </si>
-  <si>
-    <t>e_spv_036</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 36</t>
-  </si>
-  <si>
-    <t>e_spv_037</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 37</t>
-  </si>
-  <si>
-    <t>e_spv_038</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 38</t>
-  </si>
-  <si>
-    <t>e_spv_039</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 39</t>
-  </si>
-  <si>
-    <t>e_spv_040</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 40</t>
-  </si>
-  <si>
-    <t>e_spv_041</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 41</t>
-  </si>
-  <si>
-    <t>e_spv_042</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 42</t>
-  </si>
-  <si>
-    <t>e_spv_043</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 43</t>
-  </si>
-  <si>
     <t>comm-out</t>
   </si>
   <si>
@@ -1712,6 +1684,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>e_ZA11-400,e_ZA40-400,e_ZA41-400,e_ZA44-400,e_w120941269-400,e_w169647963-400,e_w169789536-400,e_w182042518-400,e_w219384657-400,e_w219384657-765,e_w545652232-400,e_w62193952-400,e_w62218063-400,e_w836844162-400,e_w90454383-400</t>
   </si>
 </sst>
 </file>
@@ -1726,7 +1701,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1874,8 +1849,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1967,6 +1949,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2181,7 +2168,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2201,8 +2188,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2594,6 +2582,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2613,8 +2602,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3007,423 +2997,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B11:V28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="14.65" thickBot="1">
-      <c r="B2" s="2" t="s">
+    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+      <c r="B11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L11" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="2:22">
-      <c r="B3" s="1" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P12" s="2">
         <v>2022</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S12" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>C4</f>
-        <v>ElcAgg_Solar</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="str">
-        <f>C5</f>
-        <v>ElcAgg_Wind</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="str">
-        <f>C6</f>
-        <v>e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="str">
-        <f>C7</f>
-        <v>h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>fossil_supply</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -3431,32 +3094,32 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>C13</f>
+        <v>ElcAgg_Solar</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -3464,37 +3127,37 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f>C14</f>
+        <v>ElcAgg_Wind</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -3506,120 +3169,455 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C15</f>
+        <v>e_demand</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
+      <c r="Q15" s="1"/>
+      <c r="V15" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C16</f>
+        <v>h_demand</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
+        <f>C19</f>
+        <v>fossil_supply</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
+        <f t="shared" ref="O17:O21" si="0">V17*3.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <f>V19*3.6</f>
+        <v>36</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="V19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="str">
+        <f>C20</f>
+        <v>renewable</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
+        <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
+      <c r="P20" s="1"/>
+      <c r="V20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
-        <f>C8</f>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <f>V22*3.6</f>
+        <v>25.2</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="V22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>C21</f>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
+        <f>V23*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="str">
+        <f>C22</f>
+        <v>solar_potential</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <f>V24*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="str">
+        <f>C23</f>
+        <v>winon_potential</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <f>V25*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="str">
+        <f>C24</f>
+        <v>winoff_potential</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <f t="shared" ref="O26" si="1">V26*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" t="str">
+        <f>C17</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-      <c r="P18">
+      <c r="L27" t="str">
+        <f>$V$28</f>
+        <v>e_ZA11-400,e_ZA40-400,e_ZA41-400,e_ZA44-400,e_w120941269-400,e_w169647963-400,e_w169789536-400,e_w182042518-400,e_w219384657-400,e_w219384657-765,e_w545652232-400,e_w62193952-400,e_w62218063-400,e_w836844162-400,e_w90454383-400</v>
+      </c>
+      <c r="P27">
         <v>0</v>
       </c>
-      <c r="Q18">
+      <c r="Q27">
         <v>3</v>
       </c>
-      <c r="R18">
+      <c r="R27">
         <v>1000</v>
       </c>
-      <c r="S18">
+      <c r="S27">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
-        <f>C9</f>
+    <row r="28" spans="2:22">
+      <c r="J28" t="str">
+        <f>C18</f>
         <v>Trd_electricity export</v>
       </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19">
+      <c r="K28" t="str">
+        <f>$V$28</f>
+        <v>e_ZA11-400,e_ZA40-400,e_ZA41-400,e_ZA44-400,e_w120941269-400,e_w169647963-400,e_w169789536-400,e_w182042518-400,e_w219384657-400,e_w219384657-765,e_w545652232-400,e_w62193952-400,e_w62218063-400,e_w836844162-400,e_w90454383-400</v>
+      </c>
+      <c r="P28">
         <v>0</v>
       </c>
-      <c r="Q19">
+      <c r="Q28">
         <v>3</v>
       </c>
-      <c r="R19">
+      <c r="R28">
         <v>1000</v>
       </c>
-      <c r="S19">
+      <c r="S28">
         <v>50</v>
+      </c>
+      <c r="V28" s="147" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -3628,158 +3626,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5417F31-D792-47CD-82F2-E942FCB1F74A}">
-  <dimension ref="B9:N13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="9" spans="2:14">
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="I10" t="s">
-        <v>164</v>
-      </c>
-      <c r="J10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" t="s">
-        <v>175</v>
-      </c>
-      <c r="M10" t="s">
-        <v>176</v>
-      </c>
-      <c r="N10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" t="s">
-        <v>167</v>
-      </c>
-      <c r="J11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11">
-        <v>0.97599999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12">
-        <v>0.92300000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" t="s">
-        <v>172</v>
-      </c>
-      <c r="J13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13">
-        <v>0.83099999999999996</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD6D8AA-F8A9-4BBE-94C7-C767CA3BCC03}">
   <dimension ref="B2:W61"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
@@ -5015,7 +4861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12EA90E-43F0-4F26-A089-D51219939B11}">
   <dimension ref="B3:Y8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -5248,9 +5094,8 @@
     <row r="8" spans="2:25" ht="17.649999999999999">
       <c r="B8" s="20"/>
       <c r="E8" s="26"/>
-      <c r="F8" t="str">
-        <f>C5</f>
-        <v>ELC</v>
+      <c r="F8" t="s">
+        <v>163</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>
@@ -5286,7 +5131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A64BB3-8019-4461-A511-24783E2ADCDE}">
   <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -5317,25 +5162,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5381,7 +5226,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5426,7 +5271,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5468,7 +5313,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6572,63 +6417,63 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0E0AAC-3309-48B7-B0B0-5ECB5F3BBB52}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B17665-3DF4-42F4-A82A-BE06FB389A5F}">
   <dimension ref="B9:M53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E10" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F10" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
         <v>166</v>
       </c>
-      <c r="H10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" t="s">
-        <v>164</v>
-      </c>
       <c r="K10" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="L10" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M10" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6637,33 +6482,33 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="K11" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="L11">
-        <v>44.158408061296171</v>
+        <v>56.429478435887411</v>
       </c>
       <c r="M11">
-        <v>0.26700187736591419</v>
+        <v>0.25207647823266571</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6672,33 +6517,33 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="L12">
-        <v>41.640744748028489</v>
+        <v>97.940509255758968</v>
       </c>
       <c r="M12">
-        <v>0.25950690766912687</v>
+        <v>0.26109049573058718</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6707,34 +6552,34 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="K13" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="L13">
-        <v>69.557753297874271</v>
+        <v>40.535152029925861</v>
       </c>
       <c r="M13">
-        <v>0.26809525602444961</v>
+        <v>0.25990698994338879</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" t="s">
         <v>182</v>
       </c>
-      <c r="C14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" t="s">
-        <v>192</v>
-      </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -6742,33 +6587,33 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K14" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="L14">
-        <v>77.590457128251174</v>
+        <v>42.823197842342175</v>
       </c>
       <c r="M14">
-        <v>0.2656822778882762</v>
+        <v>0.2553457994494347</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6777,33 +6622,33 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="K15" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="L15">
-        <v>111.98580578331888</v>
+        <v>38.657737868310825</v>
       </c>
       <c r="M15">
-        <v>0.25973395496792873</v>
+        <v>0.25368717475149188</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -6812,33 +6657,33 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" t="s">
         <v>185</v>
       </c>
-      <c r="H16" t="s">
-        <v>186</v>
-      </c>
-      <c r="J16" t="s">
-        <v>195</v>
-      </c>
       <c r="K16" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="L16">
-        <v>20.992632821866817</v>
+        <v>44.158408061296171</v>
       </c>
       <c r="M16">
-        <v>0.2464194390161232</v>
+        <v>0.26700187736591419</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6847,33 +6692,33 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="K17" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="L17">
-        <v>45.693716161926233</v>
+        <v>41.640744748028489</v>
       </c>
       <c r="M17">
-        <v>0.25377917045015252</v>
+        <v>0.25950690766912687</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6882,33 +6727,33 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H18" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="K18" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="L18">
-        <v>78.623037156613591</v>
+        <v>41.171207010167777</v>
       </c>
       <c r="M18">
-        <v>0.25949623198399602</v>
+        <v>0.26826256998951692</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6917,33 +6762,33 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K19" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="L19">
-        <v>12.282507099271958</v>
+        <v>105.97700341595768</v>
       </c>
       <c r="M19">
-        <v>0.24211756559357461</v>
+        <v>0.26626360775868613</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6952,33 +6797,33 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="K20" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="L20">
-        <v>25.835189510375479</v>
+        <v>2.3952801575716864</v>
       </c>
       <c r="M20">
-        <v>0.24847397468705551</v>
+        <v>0.23745087287451869</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6987,33 +6832,33 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H21" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="K21" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L21">
-        <v>2.3952801575716864</v>
+        <v>12.904824068159623</v>
       </c>
       <c r="M21">
-        <v>0.23745087287451869</v>
+        <v>0.2451476227155413</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -7022,33 +6867,33 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H22" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K22" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="L22">
-        <v>12.904824068159623</v>
+        <v>29.31230018687852</v>
       </c>
       <c r="M22">
-        <v>0.2451476227155413</v>
+        <v>0.2488724719138711</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -7057,33 +6902,33 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H23" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="K23" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="L23">
-        <v>29.31230018687852</v>
+        <v>22.214470816241736</v>
       </c>
       <c r="M23">
-        <v>0.2488724719138711</v>
+        <v>0.25603972465784708</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -7092,33 +6937,33 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K24" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="L24">
-        <v>22.214470816241736</v>
+        <v>24.07144255314072</v>
       </c>
       <c r="M24">
-        <v>0.25603972465784708</v>
+        <v>0.2646459198464699</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -7127,33 +6972,33 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="K25" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L25">
-        <v>24.07144255314072</v>
+        <v>2.3538967711813057</v>
       </c>
       <c r="M25">
-        <v>0.2646459198464699</v>
+        <v>0.21199843631213611</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -7162,33 +7007,33 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H26" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="K26" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="L26">
-        <v>2.3538967711813057</v>
+        <v>11.164141515843079</v>
       </c>
       <c r="M26">
-        <v>0.21199843631213611</v>
+        <v>0.228920595536487</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -7197,33 +7042,33 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H27" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="K27" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="L27">
-        <v>17.201366583026388</v>
+        <v>25.064038168331059</v>
       </c>
       <c r="M27">
-        <v>0.2220712269339048</v>
+        <v>0.23310163450256299</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -7232,33 +7077,33 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="K28" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="L28">
-        <v>4.2443357383316815</v>
+        <v>1.2149252017823031</v>
       </c>
       <c r="M28">
-        <v>0.2274955274197375</v>
+        <v>0.21170084635134989</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D29" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -7267,33 +7112,33 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K29" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="L29">
-        <v>27.7682396795086</v>
+        <v>6.780535686435802</v>
       </c>
       <c r="M29">
-        <v>0.24059130685148539</v>
+        <v>0.2232796212133317</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D30" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -7302,33 +7147,33 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="K30" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="L30">
-        <v>1.2149252017823031</v>
+        <v>4.354279652922429</v>
       </c>
       <c r="M30">
-        <v>0.21170084635134989</v>
+        <v>0.2273175886369857</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -7337,33 +7182,33 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="K31" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="L31">
-        <v>6.8904796010265494</v>
+        <v>27.7682396795086</v>
       </c>
       <c r="M31">
-        <v>0.22323444554961219</v>
+        <v>0.24059130685148539</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D32" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -7372,33 +7217,33 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="K32" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="L32">
-        <v>1.6388504698729149</v>
+        <v>11.746145248555749</v>
       </c>
       <c r="M32">
-        <v>0.18266247456258269</v>
+        <v>0.19106194324738529</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -7407,33 +7252,33 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H33" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J33" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="K33" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="L33">
-        <v>3.4061322572776196</v>
+        <v>10.151636249684735</v>
       </c>
       <c r="M33">
-        <v>0.2083777982771082</v>
+        <v>0.18815941777915471</v>
       </c>
     </row>
     <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -7442,33 +7287,33 @@
         <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H34" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J34" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K34" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="L34">
-        <v>3.2573285626193962</v>
+        <v>16.998068135490481</v>
       </c>
       <c r="M34">
-        <v>0.19652915474929389</v>
+        <v>0.19477093059803541</v>
       </c>
     </row>
     <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D35" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -7477,33 +7322,33 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J35" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K35" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="L35">
-        <v>10.303329586985814</v>
+        <v>20.691784306073561</v>
       </c>
       <c r="M35">
-        <v>0.23437547258180519</v>
+        <v>0.2073770682577383</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -7512,33 +7357,33 @@
         <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H36" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J36" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="K36" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="L36">
-        <v>2.6360968796725124</v>
+        <v>14.371597679532691</v>
       </c>
       <c r="M36">
-        <v>0.2042826035183809</v>
+        <v>0.22194550173217681</v>
       </c>
     </row>
     <row r="37" spans="2:13">
       <c r="B37" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D37" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -7547,33 +7392,33 @@
         <v>21</v>
       </c>
       <c r="G37" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H37" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J37" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="K37" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="L37">
-        <v>27.474642892253513</v>
+        <v>11.754405498479368</v>
       </c>
       <c r="M37">
-        <v>0.2302481295307893</v>
+        <v>0.21242443438078759</v>
       </c>
     </row>
     <row r="38" spans="2:13">
       <c r="B38" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D38" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -7582,33 +7427,33 @@
         <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H38" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J38" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="K38" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="L38">
-        <v>63.720446576087795</v>
+        <v>0.74876759658451164</v>
       </c>
       <c r="M38">
-        <v>0.23318065257061349</v>
+        <v>0.1821501216215636</v>
       </c>
     </row>
     <row r="39" spans="2:13">
       <c r="B39" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -7617,33 +7462,33 @@
         <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H39" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J39" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="K39" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="L39">
-        <v>29.239068847577361</v>
+        <v>3.3995048866585469</v>
       </c>
       <c r="M39">
-        <v>0.22460706804417219</v>
+        <v>0.19260723608401659</v>
       </c>
     </row>
     <row r="40" spans="2:13">
       <c r="B40" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D40" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -7652,33 +7497,33 @@
         <v>21</v>
       </c>
       <c r="G40" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H40" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J40" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="K40" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="L40">
-        <v>19.549817854653909</v>
+        <v>1.990913758023849</v>
       </c>
       <c r="M40">
-        <v>0.2287196564423056</v>
+        <v>0.19325827910937171</v>
       </c>
     </row>
     <row r="41" spans="2:13">
       <c r="B41" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C41" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D41" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -7687,33 +7532,33 @@
         <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H41" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J41" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="K41" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="L41">
-        <v>11.754405498479368</v>
+        <v>5.0921677517335207</v>
       </c>
       <c r="M41">
-        <v>0.21242443438078759</v>
+        <v>0.17874238508217991</v>
       </c>
     </row>
     <row r="42" spans="2:13">
       <c r="B42" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C42" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D42" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -7722,33 +7567,33 @@
         <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H42" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J42" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="K42" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L42">
-        <v>8.4913001207572822</v>
+        <v>1.6388504698729149</v>
       </c>
       <c r="M42">
-        <v>0.22997773913066369</v>
+        <v>0.18266247456258269</v>
       </c>
     </row>
     <row r="43" spans="2:13">
       <c r="B43" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D43" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
@@ -7757,33 +7602,33 @@
         <v>21</v>
       </c>
       <c r="G43" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H43" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J43" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="K43" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="L43">
-        <v>15.555030417058223</v>
+        <v>3.4061322572776196</v>
       </c>
       <c r="M43">
-        <v>0.22714237227495959</v>
+        <v>0.2083777982771082</v>
       </c>
     </row>
     <row r="44" spans="2:13">
       <c r="B44" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D44" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -7792,33 +7637,33 @@
         <v>21</v>
       </c>
       <c r="G44" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H44" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J44" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="K44" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="L44">
-        <v>31.18938712557021</v>
+        <v>3.2573285626193962</v>
       </c>
       <c r="M44">
-        <v>0.24081602966875409</v>
+        <v>0.19652915474929389</v>
       </c>
     </row>
     <row r="45" spans="2:13">
       <c r="B45" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D45" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -7827,33 +7672,33 @@
         <v>21</v>
       </c>
       <c r="G45" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H45" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J45" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="K45" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="L45">
-        <v>28.757070855030403</v>
+        <v>10.303329586985814</v>
       </c>
       <c r="M45">
-        <v>0.24859980825566219</v>
+        <v>0.23437547258180519</v>
       </c>
     </row>
     <row r="46" spans="2:13">
       <c r="B46" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C46" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D46" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -7862,33 +7707,33 @@
         <v>21</v>
       </c>
       <c r="G46" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H46" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J46" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="K46" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="L46">
-        <v>4.1482724832430584</v>
+        <v>2.6360968796725124</v>
       </c>
       <c r="M46">
-        <v>0.19071971579818939</v>
+        <v>0.2042826035183809</v>
       </c>
     </row>
     <row r="47" spans="2:13">
       <c r="B47" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C47" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D47" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -7897,33 +7742,33 @@
         <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H47" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J47" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="K47" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="L47">
-        <v>1.990913758023849</v>
+        <v>27.474642892253513</v>
       </c>
       <c r="M47">
-        <v>0.19325827910937171</v>
+        <v>0.2302481295307893</v>
       </c>
     </row>
     <row r="48" spans="2:13">
       <c r="B48" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -7932,33 +7777,33 @@
         <v>21</v>
       </c>
       <c r="G48" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H48" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J48" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="K48" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="L48">
-        <v>5.0921677517335207</v>
+        <v>63.720446576087795</v>
       </c>
       <c r="M48">
-        <v>0.17874238508217991</v>
+        <v>0.23318065257061349</v>
       </c>
     </row>
     <row r="49" spans="2:13">
       <c r="B49" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D49" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -7967,33 +7812,33 @@
         <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H49" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J49" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="K49" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="L49">
-        <v>13.433952485076439</v>
+        <v>29.239068847577361</v>
       </c>
       <c r="M49">
-        <v>0.1954257377783494</v>
+        <v>0.22460706804417219</v>
       </c>
     </row>
     <row r="50" spans="2:13">
       <c r="B50" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D50" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -8002,33 +7847,33 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H50" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J50" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="K50" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="L50">
-        <v>20.691784306073561</v>
+        <v>19.549817854653909</v>
       </c>
       <c r="M50">
-        <v>0.2073770682577383</v>
+        <v>0.2287196564423056</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C51" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D51" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
@@ -8037,33 +7882,33 @@
         <v>21</v>
       </c>
       <c r="G51" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H51" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J51" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="K51" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L51">
-        <v>7.6462314473446558</v>
+        <v>28.757070855030403</v>
       </c>
       <c r="M51">
-        <v>0.21510168827728471</v>
+        <v>0.24859980825566219</v>
       </c>
     </row>
     <row r="52" spans="2:13">
       <c r="B52" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="D52" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -8072,33 +7917,33 @@
         <v>21</v>
       </c>
       <c r="G52" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J52" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K52" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="L52">
-        <v>8.7729839062908663</v>
+        <v>25.892135224655235</v>
       </c>
       <c r="M52">
-        <v>0.1862106256227114</v>
+        <v>0.24134502600928109</v>
       </c>
     </row>
     <row r="53" spans="2:13">
       <c r="B53" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D53" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -8107,22 +7952,2244 @@
         <v>21</v>
       </c>
       <c r="G53" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H53" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J53" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="K53" t="s">
+        <v>307</v>
+      </c>
+      <c r="L53">
+        <v>21.239563863148575</v>
+      </c>
+      <c r="M53">
+        <v>0.23194852600613919</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFCC9392-012B-4171-B0A5-25803B8C1DBD}">
+  <dimension ref="B9:Z52"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="9" spans="2:26">
+      <c r="B9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J9" t="s">
+        <v>261</v>
+      </c>
+      <c r="O9" t="s">
+        <v>164</v>
+      </c>
+      <c r="W9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26">
+      <c r="B10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" t="s">
+        <v>262</v>
+      </c>
+      <c r="L10" t="s">
+        <v>263</v>
+      </c>
+      <c r="M10" t="s">
+        <v>264</v>
+      </c>
+      <c r="O10" t="s">
+        <v>165</v>
+      </c>
+      <c r="P10" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>167</v>
+      </c>
+      <c r="R10" t="s">
+        <v>168</v>
+      </c>
+      <c r="S10" t="s">
+        <v>169</v>
+      </c>
+      <c r="T10" t="s">
+        <v>170</v>
+      </c>
+      <c r="U10" t="s">
+        <v>171</v>
+      </c>
+      <c r="W10" t="s">
+        <v>166</v>
+      </c>
+      <c r="X10" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26">
+      <c r="B11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" t="s">
+        <v>308</v>
+      </c>
+      <c r="D11" t="s">
+        <v>309</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" t="s">
+        <v>308</v>
+      </c>
+      <c r="K11" t="s">
+        <v>392</v>
+      </c>
+      <c r="L11">
+        <v>9.3348685452622586</v>
+      </c>
+      <c r="M11">
+        <v>0.1843319915380067</v>
+      </c>
+      <c r="O11" t="s">
+        <v>172</v>
+      </c>
+      <c r="P11" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>435</v>
+      </c>
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>175</v>
+      </c>
+      <c r="U11" t="s">
+        <v>176</v>
+      </c>
+      <c r="W11" t="s">
+        <v>434</v>
+      </c>
+      <c r="X11" t="s">
+        <v>474</v>
+      </c>
+      <c r="Y11">
+        <v>22.356000000000002</v>
+      </c>
+      <c r="Z11">
+        <v>0.54621145523239889</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26">
+      <c r="B12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" t="s">
+        <v>310</v>
+      </c>
+      <c r="K12" t="s">
+        <v>393</v>
+      </c>
+      <c r="L12">
+        <v>41.625170147271362</v>
+      </c>
+      <c r="M12">
+        <v>0.2641821193468662</v>
+      </c>
+      <c r="O12" t="s">
+        <v>172</v>
+      </c>
+      <c r="P12" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>437</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
+        <v>175</v>
+      </c>
+      <c r="U12" t="s">
+        <v>176</v>
+      </c>
+      <c r="W12" t="s">
+        <v>436</v>
+      </c>
+      <c r="X12" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y12">
+        <v>71.144999999999996</v>
+      </c>
+      <c r="Z12">
+        <v>0.51608117349821281</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26">
+      <c r="B13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" t="s">
+        <v>312</v>
+      </c>
+      <c r="K13" t="s">
+        <v>394</v>
+      </c>
+      <c r="L13">
+        <v>18.676901648902387</v>
+      </c>
+      <c r="M13">
+        <v>0.1448045738501898</v>
+      </c>
+      <c r="O13" t="s">
+        <v>172</v>
+      </c>
+      <c r="P13" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>439</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>175</v>
+      </c>
+      <c r="U13" t="s">
+        <v>176</v>
+      </c>
+      <c r="W13" t="s">
+        <v>438</v>
+      </c>
+      <c r="X13" t="s">
+        <v>476</v>
+      </c>
+      <c r="Y13">
+        <v>20.269500000000001</v>
+      </c>
+      <c r="Z13">
+        <v>0.3762889566749637</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26">
+      <c r="B14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D14" t="s">
+        <v>315</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J14" t="s">
+        <v>314</v>
+      </c>
+      <c r="K14" t="s">
+        <v>395</v>
+      </c>
+      <c r="L14">
+        <v>17.522570055216363</v>
+      </c>
+      <c r="M14">
+        <v>0.14724526375320399</v>
+      </c>
+      <c r="O14" t="s">
+        <v>172</v>
+      </c>
+      <c r="P14" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>441</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>175</v>
+      </c>
+      <c r="U14" t="s">
+        <v>176</v>
+      </c>
+      <c r="W14" t="s">
+        <v>440</v>
+      </c>
+      <c r="X14" t="s">
+        <v>477</v>
+      </c>
+      <c r="Y14">
+        <v>91.751999999999995</v>
+      </c>
+      <c r="Z14">
+        <v>0.52990963262679169</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26">
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" t="s">
         <v>316</v>
       </c>
-      <c r="L53">
-        <v>15.310260898969792</v>
-      </c>
-      <c r="M53">
-        <v>0.1913508090835456</v>
+      <c r="D15" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="J15" t="s">
+        <v>316</v>
+      </c>
+      <c r="K15" t="s">
+        <v>396</v>
+      </c>
+      <c r="L15">
+        <v>14.248215224493222</v>
+      </c>
+      <c r="M15">
+        <v>0.2270019606139384</v>
+      </c>
+      <c r="O15" t="s">
+        <v>172</v>
+      </c>
+      <c r="P15" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>443</v>
+      </c>
+      <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
+        <v>175</v>
+      </c>
+      <c r="U15" t="s">
+        <v>176</v>
+      </c>
+      <c r="W15" t="s">
+        <v>442</v>
+      </c>
+      <c r="X15" t="s">
+        <v>478</v>
+      </c>
+      <c r="Y15">
+        <v>9.2227499999999996</v>
+      </c>
+      <c r="Z15">
+        <v>0.37281254683293108</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26">
+      <c r="B16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C16" t="s">
+        <v>318</v>
+      </c>
+      <c r="D16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" t="s">
+        <v>318</v>
+      </c>
+      <c r="K16" t="s">
+        <v>397</v>
+      </c>
+      <c r="L16">
+        <v>60.246276232111249</v>
+      </c>
+      <c r="M16">
+        <v>0.29796998234161798</v>
+      </c>
+      <c r="O16" t="s">
+        <v>172</v>
+      </c>
+      <c r="P16" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>445</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>175</v>
+      </c>
+      <c r="U16" t="s">
+        <v>176</v>
+      </c>
+      <c r="W16" t="s">
+        <v>444</v>
+      </c>
+      <c r="X16" t="s">
+        <v>479</v>
+      </c>
+      <c r="Y16">
+        <v>66.892499999999998</v>
+      </c>
+      <c r="Z16">
+        <v>0.50083145791048822</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26">
+      <c r="B17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" t="s">
+        <v>320</v>
+      </c>
+      <c r="D17" t="s">
+        <v>321</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" t="s">
+        <v>320</v>
+      </c>
+      <c r="K17" t="s">
+        <v>398</v>
+      </c>
+      <c r="L17">
+        <v>7.6187600542008829</v>
+      </c>
+      <c r="M17">
+        <v>0.1016094115504282</v>
+      </c>
+      <c r="O17" t="s">
+        <v>172</v>
+      </c>
+      <c r="P17" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>447</v>
+      </c>
+      <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
+        <v>175</v>
+      </c>
+      <c r="U17" t="s">
+        <v>176</v>
+      </c>
+      <c r="W17" t="s">
+        <v>446</v>
+      </c>
+      <c r="X17" t="s">
+        <v>480</v>
+      </c>
+      <c r="Y17">
+        <v>16.734749999999998</v>
+      </c>
+      <c r="Z17">
+        <v>0.42736446278598761</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26">
+      <c r="B18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" t="s">
+        <v>322</v>
+      </c>
+      <c r="D18" t="s">
+        <v>323</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" t="s">
+        <v>176</v>
+      </c>
+      <c r="J18" t="s">
+        <v>322</v>
+      </c>
+      <c r="K18" t="s">
+        <v>399</v>
+      </c>
+      <c r="L18">
+        <v>13.317870473911716</v>
+      </c>
+      <c r="M18">
+        <v>0.20062430489929889</v>
+      </c>
+      <c r="O18" t="s">
+        <v>172</v>
+      </c>
+      <c r="P18" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>449</v>
+      </c>
+      <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>175</v>
+      </c>
+      <c r="U18" t="s">
+        <v>176</v>
+      </c>
+      <c r="W18" t="s">
+        <v>448</v>
+      </c>
+      <c r="X18" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y18">
+        <v>6.2925000000000004</v>
+      </c>
+      <c r="Z18">
+        <v>0.36116730033911121</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26">
+      <c r="B19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" t="s">
+        <v>324</v>
+      </c>
+      <c r="D19" t="s">
+        <v>325</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J19" t="s">
+        <v>324</v>
+      </c>
+      <c r="K19" t="s">
+        <v>400</v>
+      </c>
+      <c r="L19">
+        <v>15.921767829784981</v>
+      </c>
+      <c r="M19">
+        <v>0.2098918338026157</v>
+      </c>
+      <c r="O19" t="s">
+        <v>172</v>
+      </c>
+      <c r="P19" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>451</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>175</v>
+      </c>
+      <c r="U19" t="s">
+        <v>176</v>
+      </c>
+      <c r="W19" t="s">
+        <v>450</v>
+      </c>
+      <c r="X19" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y19">
+        <v>8.7997499999999995</v>
+      </c>
+      <c r="Z19">
+        <v>0.37331655841332761</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26">
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" t="s">
+        <v>326</v>
+      </c>
+      <c r="D20" t="s">
+        <v>327</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" t="s">
+        <v>326</v>
+      </c>
+      <c r="K20" t="s">
+        <v>401</v>
+      </c>
+      <c r="L20">
+        <v>1.242396749224558</v>
+      </c>
+      <c r="M20">
+        <v>8.5955872642622402E-2</v>
+      </c>
+      <c r="O20" t="s">
+        <v>172</v>
+      </c>
+      <c r="P20" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>453</v>
+      </c>
+      <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
+        <v>175</v>
+      </c>
+      <c r="U20" t="s">
+        <v>176</v>
+      </c>
+      <c r="W20" t="s">
+        <v>452</v>
+      </c>
+      <c r="X20" t="s">
+        <v>483</v>
+      </c>
+      <c r="Y20">
+        <v>12.29025</v>
+      </c>
+      <c r="Z20">
+        <v>0.41736483903193727</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26">
+      <c r="B21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" t="s">
+        <v>328</v>
+      </c>
+      <c r="K21" t="s">
+        <v>402</v>
+      </c>
+      <c r="L21">
+        <v>11.156586435503245</v>
+      </c>
+      <c r="M21">
+        <v>0.1458988949348993</v>
+      </c>
+      <c r="O21" t="s">
+        <v>172</v>
+      </c>
+      <c r="P21" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>455</v>
+      </c>
+      <c r="R21" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s">
+        <v>175</v>
+      </c>
+      <c r="U21" t="s">
+        <v>176</v>
+      </c>
+      <c r="W21" t="s">
+        <v>454</v>
+      </c>
+      <c r="X21" t="s">
+        <v>484</v>
+      </c>
+      <c r="Y21">
+        <v>7.4317500000000001</v>
+      </c>
+      <c r="Z21">
+        <v>0.50389818070132053</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26">
+      <c r="B22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" t="s">
+        <v>330</v>
+      </c>
+      <c r="D22" t="s">
+        <v>331</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" t="s">
+        <v>330</v>
+      </c>
+      <c r="K22" t="s">
+        <v>403</v>
+      </c>
+      <c r="L22">
+        <v>6.3773535033999496</v>
+      </c>
+      <c r="M22">
+        <v>0.26612703444830588</v>
+      </c>
+      <c r="O22" t="s">
+        <v>172</v>
+      </c>
+      <c r="P22" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>457</v>
+      </c>
+      <c r="R22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s">
+        <v>175</v>
+      </c>
+      <c r="U22" t="s">
+        <v>176</v>
+      </c>
+      <c r="W22" t="s">
+        <v>456</v>
+      </c>
+      <c r="X22" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y22">
+        <v>21.263249999999999</v>
+      </c>
+      <c r="Z22">
+        <v>0.49047893511766888</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26">
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" t="s">
+        <v>332</v>
+      </c>
+      <c r="D23" t="s">
+        <v>333</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" t="s">
+        <v>332</v>
+      </c>
+      <c r="K23" t="s">
+        <v>404</v>
+      </c>
+      <c r="L23">
+        <v>4.8861340927283274</v>
+      </c>
+      <c r="M23">
+        <v>0.30360257079112291</v>
+      </c>
+      <c r="O23" t="s">
+        <v>172</v>
+      </c>
+      <c r="P23" t="s">
+        <v>458</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>459</v>
+      </c>
+      <c r="R23" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23" t="s">
+        <v>21</v>
+      </c>
+      <c r="T23" t="s">
+        <v>175</v>
+      </c>
+      <c r="U23" t="s">
+        <v>176</v>
+      </c>
+      <c r="W23" t="s">
+        <v>458</v>
+      </c>
+      <c r="X23" t="s">
+        <v>486</v>
+      </c>
+      <c r="Y23">
+        <v>36.704999999999998</v>
+      </c>
+      <c r="Z23">
+        <v>0.51263869178343313</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26">
+      <c r="B24" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" t="s">
+        <v>334</v>
+      </c>
+      <c r="D24" t="s">
+        <v>335</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" t="s">
+        <v>334</v>
+      </c>
+      <c r="K24" t="s">
+        <v>405</v>
+      </c>
+      <c r="L24">
+        <v>13.571087213989722</v>
+      </c>
+      <c r="M24">
+        <v>0.19929607412876171</v>
+      </c>
+      <c r="O24" t="s">
+        <v>172</v>
+      </c>
+      <c r="P24" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>461</v>
+      </c>
+      <c r="R24" t="s">
+        <v>10</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" t="s">
+        <v>175</v>
+      </c>
+      <c r="U24" t="s">
+        <v>176</v>
+      </c>
+      <c r="W24" t="s">
+        <v>460</v>
+      </c>
+      <c r="X24" t="s">
+        <v>487</v>
+      </c>
+      <c r="Y24">
+        <v>72.104249999999993</v>
+      </c>
+      <c r="Z24">
+        <v>0.51445152950381501</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26">
+      <c r="B25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" t="s">
+        <v>336</v>
+      </c>
+      <c r="D25" t="s">
+        <v>337</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" t="s">
+        <v>176</v>
+      </c>
+      <c r="J25" t="s">
+        <v>336</v>
+      </c>
+      <c r="K25" t="s">
+        <v>406</v>
+      </c>
+      <c r="L25">
+        <v>2.8310936025572326</v>
+      </c>
+      <c r="M25">
+        <v>0.11880817254789069</v>
+      </c>
+      <c r="O25" t="s">
+        <v>172</v>
+      </c>
+      <c r="P25" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>463</v>
+      </c>
+      <c r="R25" t="s">
+        <v>10</v>
+      </c>
+      <c r="S25" t="s">
+        <v>21</v>
+      </c>
+      <c r="T25" t="s">
+        <v>175</v>
+      </c>
+      <c r="U25" t="s">
+        <v>176</v>
+      </c>
+      <c r="W25" t="s">
+        <v>462</v>
+      </c>
+      <c r="X25" t="s">
+        <v>488</v>
+      </c>
+      <c r="Y25">
+        <v>7.6185</v>
+      </c>
+      <c r="Z25">
+        <v>0.3673526052541094</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26">
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" t="s">
+        <v>339</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J26" t="s">
+        <v>338</v>
+      </c>
+      <c r="K26" t="s">
+        <v>407</v>
+      </c>
+      <c r="L26">
+        <v>9.8725175016467617</v>
+      </c>
+      <c r="M26">
+        <v>0.26308084673963789</v>
+      </c>
+      <c r="O26" t="s">
+        <v>172</v>
+      </c>
+      <c r="P26" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>465</v>
+      </c>
+      <c r="R26" t="s">
+        <v>10</v>
+      </c>
+      <c r="S26" t="s">
+        <v>21</v>
+      </c>
+      <c r="T26" t="s">
+        <v>175</v>
+      </c>
+      <c r="U26" t="s">
+        <v>176</v>
+      </c>
+      <c r="W26" t="s">
+        <v>464</v>
+      </c>
+      <c r="X26" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y26">
+        <v>38.655749999999998</v>
+      </c>
+      <c r="Z26">
+        <v>0.54519508896051261</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26">
+      <c r="B27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" t="s">
+        <v>340</v>
+      </c>
+      <c r="D27" t="s">
+        <v>341</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" t="s">
+        <v>340</v>
+      </c>
+      <c r="K27" t="s">
+        <v>408</v>
+      </c>
+      <c r="L27">
+        <v>2.1088679510249264</v>
+      </c>
+      <c r="M27">
+        <v>9.3570387474760999E-2</v>
+      </c>
+      <c r="O27" t="s">
+        <v>172</v>
+      </c>
+      <c r="P27" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>467</v>
+      </c>
+      <c r="R27" t="s">
+        <v>10</v>
+      </c>
+      <c r="S27" t="s">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s">
+        <v>175</v>
+      </c>
+      <c r="U27" t="s">
+        <v>176</v>
+      </c>
+      <c r="W27" t="s">
+        <v>466</v>
+      </c>
+      <c r="X27" t="s">
+        <v>490</v>
+      </c>
+      <c r="Y27">
+        <v>25.178999999999998</v>
+      </c>
+      <c r="Z27">
+        <v>0.48943290731950911</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26">
+      <c r="B28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" t="s">
+        <v>342</v>
+      </c>
+      <c r="D28" t="s">
+        <v>343</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" t="s">
+        <v>342</v>
+      </c>
+      <c r="K28" t="s">
+        <v>409</v>
+      </c>
+      <c r="L28">
+        <v>3.109672262974355</v>
+      </c>
+      <c r="M28">
+        <v>0.32076749760644679</v>
+      </c>
+      <c r="O28" t="s">
+        <v>172</v>
+      </c>
+      <c r="P28" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>469</v>
+      </c>
+      <c r="R28" t="s">
+        <v>10</v>
+      </c>
+      <c r="S28" t="s">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s">
+        <v>175</v>
+      </c>
+      <c r="U28" t="s">
+        <v>176</v>
+      </c>
+      <c r="W28" t="s">
+        <v>468</v>
+      </c>
+      <c r="X28" t="s">
+        <v>491</v>
+      </c>
+      <c r="Y28">
+        <v>30.076499999999999</v>
+      </c>
+      <c r="Z28">
+        <v>0.43612324739653358</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26">
+      <c r="B29" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" t="s">
+        <v>344</v>
+      </c>
+      <c r="D29" t="s">
+        <v>345</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" t="s">
+        <v>176</v>
+      </c>
+      <c r="J29" t="s">
+        <v>344</v>
+      </c>
+      <c r="K29" t="s">
+        <v>410</v>
+      </c>
+      <c r="L29">
+        <v>2.2821221811848558</v>
+      </c>
+      <c r="M29">
+        <v>0.14789509056852229</v>
+      </c>
+      <c r="O29" t="s">
+        <v>172</v>
+      </c>
+      <c r="P29" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>471</v>
+      </c>
+      <c r="R29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" t="s">
+        <v>21</v>
+      </c>
+      <c r="T29" t="s">
+        <v>175</v>
+      </c>
+      <c r="U29" t="s">
+        <v>176</v>
+      </c>
+      <c r="W29" t="s">
+        <v>470</v>
+      </c>
+      <c r="X29" t="s">
+        <v>492</v>
+      </c>
+      <c r="Y29">
+        <v>69.197999999999993</v>
+      </c>
+      <c r="Z29">
+        <v>0.45139689289404111</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26">
+      <c r="B30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" t="s">
+        <v>346</v>
+      </c>
+      <c r="D30" t="s">
+        <v>347</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
+        <v>346</v>
+      </c>
+      <c r="K30" t="s">
+        <v>411</v>
+      </c>
+      <c r="L30">
+        <v>6.0746622584304504</v>
+      </c>
+      <c r="M30">
+        <v>0.17149549523455249</v>
+      </c>
+      <c r="O30" t="s">
+        <v>172</v>
+      </c>
+      <c r="P30" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>473</v>
+      </c>
+      <c r="R30" t="s">
+        <v>10</v>
+      </c>
+      <c r="S30" t="s">
+        <v>21</v>
+      </c>
+      <c r="T30" t="s">
+        <v>175</v>
+      </c>
+      <c r="U30" t="s">
+        <v>176</v>
+      </c>
+      <c r="W30" t="s">
+        <v>472</v>
+      </c>
+      <c r="X30" t="s">
+        <v>493</v>
+      </c>
+      <c r="Y30">
+        <v>24.058499999999999</v>
+      </c>
+      <c r="Z30">
+        <v>0.29027769463508862</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26">
+      <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
+        <v>348</v>
+      </c>
+      <c r="D31" t="s">
+        <v>349</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" t="s">
+        <v>348</v>
+      </c>
+      <c r="K31" t="s">
+        <v>412</v>
+      </c>
+      <c r="L31">
+        <v>16.31886018972364</v>
+      </c>
+      <c r="M31">
+        <v>0.2166175963211332</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26">
+      <c r="B32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s">
+        <v>350</v>
+      </c>
+      <c r="D32" t="s">
+        <v>351</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" t="s">
+        <v>350</v>
+      </c>
+      <c r="K32" t="s">
+        <v>413</v>
+      </c>
+      <c r="L32">
+        <v>1.1455000262712256</v>
+      </c>
+      <c r="M32">
+        <v>0.10417096817583441</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>352</v>
+      </c>
+      <c r="D33" t="s">
+        <v>353</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" t="s">
+        <v>352</v>
+      </c>
+      <c r="K33" t="s">
+        <v>414</v>
+      </c>
+      <c r="L33">
+        <v>11.364861678100382</v>
+      </c>
+      <c r="M33">
+        <v>0.2050393536459105</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
+      <c r="B34" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" t="s">
+        <v>354</v>
+      </c>
+      <c r="D34" t="s">
+        <v>355</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" t="s">
+        <v>354</v>
+      </c>
+      <c r="K34" t="s">
+        <v>415</v>
+      </c>
+      <c r="L34">
+        <v>7.8135900005455872</v>
+      </c>
+      <c r="M34">
+        <v>0.21608568854715859</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
+      <c r="B35" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" t="s">
+        <v>356</v>
+      </c>
+      <c r="D35" t="s">
+        <v>357</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" t="s">
+        <v>356</v>
+      </c>
+      <c r="K35" t="s">
+        <v>416</v>
+      </c>
+      <c r="L35">
+        <v>1.3654604103287289</v>
+      </c>
+      <c r="M35">
+        <v>0.143845838858737</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="B36" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" t="s">
+        <v>358</v>
+      </c>
+      <c r="D36" t="s">
+        <v>359</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" t="s">
+        <v>358</v>
+      </c>
+      <c r="K36" t="s">
+        <v>417</v>
+      </c>
+      <c r="L36">
+        <v>2.222863284436507</v>
+      </c>
+      <c r="M36">
+        <v>0.1070354092669597</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
+      <c r="B37" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" t="s">
+        <v>360</v>
+      </c>
+      <c r="D37" t="s">
+        <v>361</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" t="s">
+        <v>176</v>
+      </c>
+      <c r="J37" t="s">
+        <v>360</v>
+      </c>
+      <c r="K37" t="s">
+        <v>418</v>
+      </c>
+      <c r="L37">
+        <v>9.7399044969678972</v>
+      </c>
+      <c r="M37">
+        <v>0.22472775896605149</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13">
+      <c r="B38" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" t="s">
+        <v>362</v>
+      </c>
+      <c r="D38" t="s">
+        <v>363</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" t="s">
+        <v>175</v>
+      </c>
+      <c r="H38" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" t="s">
+        <v>362</v>
+      </c>
+      <c r="K38" t="s">
+        <v>419</v>
+      </c>
+      <c r="L38">
+        <v>11.047069314867423</v>
+      </c>
+      <c r="M38">
+        <v>0.23523818012163661</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13">
+      <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" t="s">
+        <v>364</v>
+      </c>
+      <c r="D39" t="s">
+        <v>365</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" t="s">
+        <v>176</v>
+      </c>
+      <c r="J39" t="s">
+        <v>364</v>
+      </c>
+      <c r="K39" t="s">
+        <v>420</v>
+      </c>
+      <c r="L39">
+        <v>26.32580391715549</v>
+      </c>
+      <c r="M39">
+        <v>0.28020228387492641</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
+      <c r="B40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" t="s">
+        <v>366</v>
+      </c>
+      <c r="D40" t="s">
+        <v>367</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" t="s">
+        <v>366</v>
+      </c>
+      <c r="K40" t="s">
+        <v>421</v>
+      </c>
+      <c r="L40">
+        <v>13.093319261533304</v>
+      </c>
+      <c r="M40">
+        <v>0.23411117543992219</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13">
+      <c r="B41" t="s">
+        <v>172</v>
+      </c>
+      <c r="C41" t="s">
+        <v>368</v>
+      </c>
+      <c r="D41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" t="s">
+        <v>175</v>
+      </c>
+      <c r="H41" t="s">
+        <v>176</v>
+      </c>
+      <c r="J41" t="s">
+        <v>368</v>
+      </c>
+      <c r="K41" t="s">
+        <v>422</v>
+      </c>
+      <c r="L41">
+        <v>12.996823777257559</v>
+      </c>
+      <c r="M41">
+        <v>0.2721920265122556</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13">
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" t="s">
+        <v>370</v>
+      </c>
+      <c r="D42" t="s">
+        <v>371</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H42" t="s">
+        <v>176</v>
+      </c>
+      <c r="J42" t="s">
+        <v>370</v>
+      </c>
+      <c r="K42" t="s">
+        <v>423</v>
+      </c>
+      <c r="L42">
+        <v>24.694469143848224</v>
+      </c>
+      <c r="M42">
+        <v>0.28623389287532353</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13">
+      <c r="B43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" t="s">
+        <v>372</v>
+      </c>
+      <c r="D43" t="s">
+        <v>373</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" t="s">
+        <v>175</v>
+      </c>
+      <c r="H43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J43" t="s">
+        <v>372</v>
+      </c>
+      <c r="K43" t="s">
+        <v>424</v>
+      </c>
+      <c r="L43">
+        <v>28.748060997363154</v>
+      </c>
+      <c r="M43">
+        <v>0.3484200860985141</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13">
+      <c r="B44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" t="s">
+        <v>374</v>
+      </c>
+      <c r="D44" t="s">
+        <v>375</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" t="s">
+        <v>175</v>
+      </c>
+      <c r="H44" t="s">
+        <v>176</v>
+      </c>
+      <c r="J44" t="s">
+        <v>374</v>
+      </c>
+      <c r="K44" t="s">
+        <v>425</v>
+      </c>
+      <c r="L44">
+        <v>27.436549011428941</v>
+      </c>
+      <c r="M44">
+        <v>0.29648623812476937</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13">
+      <c r="B45" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" t="s">
+        <v>376</v>
+      </c>
+      <c r="D45" t="s">
+        <v>377</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" t="s">
+        <v>175</v>
+      </c>
+      <c r="H45" t="s">
+        <v>176</v>
+      </c>
+      <c r="J45" t="s">
+        <v>376</v>
+      </c>
+      <c r="K45" t="s">
+        <v>426</v>
+      </c>
+      <c r="L45">
+        <v>11.262860315683808</v>
+      </c>
+      <c r="M45">
+        <v>0.370916188296673</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13">
+      <c r="B46" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" t="s">
+        <v>378</v>
+      </c>
+      <c r="D46" t="s">
+        <v>379</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" t="s">
+        <v>175</v>
+      </c>
+      <c r="H46" t="s">
+        <v>176</v>
+      </c>
+      <c r="J46" t="s">
+        <v>378</v>
+      </c>
+      <c r="K46" t="s">
+        <v>427</v>
+      </c>
+      <c r="L46">
+        <v>34.610640160809844</v>
+      </c>
+      <c r="M46">
+        <v>0.31938677936207349</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13">
+      <c r="B47" t="s">
+        <v>172</v>
+      </c>
+      <c r="C47" t="s">
+        <v>380</v>
+      </c>
+      <c r="D47" t="s">
+        <v>381</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" t="s">
+        <v>175</v>
+      </c>
+      <c r="H47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J47" t="s">
+        <v>380</v>
+      </c>
+      <c r="K47" t="s">
+        <v>428</v>
+      </c>
+      <c r="L47">
+        <v>22.57598984879677</v>
+      </c>
+      <c r="M47">
+        <v>0.23211275790412131</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13">
+      <c r="B48" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" t="s">
+        <v>382</v>
+      </c>
+      <c r="D48" t="s">
+        <v>383</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>176</v>
+      </c>
+      <c r="J48" t="s">
+        <v>382</v>
+      </c>
+      <c r="K48" t="s">
+        <v>429</v>
+      </c>
+      <c r="L48">
+        <v>20.256717029567771</v>
+      </c>
+      <c r="M48">
+        <v>0.18932181859163921</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13">
+      <c r="B49" t="s">
+        <v>172</v>
+      </c>
+      <c r="C49" t="s">
+        <v>384</v>
+      </c>
+      <c r="D49" t="s">
+        <v>385</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" t="s">
+        <v>175</v>
+      </c>
+      <c r="H49" t="s">
+        <v>176</v>
+      </c>
+      <c r="J49" t="s">
+        <v>384</v>
+      </c>
+      <c r="K49" t="s">
+        <v>430</v>
+      </c>
+      <c r="L49">
+        <v>63.11239557797159</v>
+      </c>
+      <c r="M49">
+        <v>0.40984504679108119</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13">
+      <c r="B50" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" t="s">
+        <v>386</v>
+      </c>
+      <c r="D50" t="s">
+        <v>387</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J50" t="s">
+        <v>386</v>
+      </c>
+      <c r="K50" t="s">
+        <v>431</v>
+      </c>
+      <c r="L50">
+        <v>38.222782480143309</v>
+      </c>
+      <c r="M50">
+        <v>0.33995720411689029</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
+      <c r="B51" t="s">
+        <v>172</v>
+      </c>
+      <c r="C51" t="s">
+        <v>388</v>
+      </c>
+      <c r="D51" t="s">
+        <v>389</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" t="s">
+        <v>175</v>
+      </c>
+      <c r="H51" t="s">
+        <v>176</v>
+      </c>
+      <c r="J51" t="s">
+        <v>388</v>
+      </c>
+      <c r="K51" t="s">
+        <v>432</v>
+      </c>
+      <c r="L51">
+        <v>41.926633570495007</v>
+      </c>
+      <c r="M51">
+        <v>0.33623081374544261</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13">
+      <c r="B52" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" t="s">
+        <v>390</v>
+      </c>
+      <c r="D52" t="s">
+        <v>391</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" t="s">
+        <v>175</v>
+      </c>
+      <c r="H52" t="s">
+        <v>176</v>
+      </c>
+      <c r="J52" t="s">
+        <v>390</v>
+      </c>
+      <c r="K52" t="s">
+        <v>433</v>
+      </c>
+      <c r="L52">
+        <v>47.281374191365337</v>
+      </c>
+      <c r="M52">
+        <v>0.31961940066535188</v>
       </c>
     </row>
   </sheetData>
@@ -8131,2249 +10198,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290F90CE-8AEA-4BA7-9BB2-6D28B95526E3}">
-  <dimension ref="B9:Z52"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="9" spans="2:26">
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J9" t="s">
-        <v>174</v>
-      </c>
-      <c r="O9" t="s">
-        <v>163</v>
-      </c>
-      <c r="W9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:26">
-      <c r="B10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K10" t="s">
-        <v>271</v>
-      </c>
-      <c r="L10" t="s">
-        <v>272</v>
-      </c>
-      <c r="M10" t="s">
-        <v>273</v>
-      </c>
-      <c r="O10" t="s">
-        <v>178</v>
-      </c>
-      <c r="P10" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>165</v>
-      </c>
-      <c r="R10" t="s">
-        <v>179</v>
-      </c>
-      <c r="S10" t="s">
-        <v>180</v>
-      </c>
-      <c r="T10" t="s">
-        <v>166</v>
-      </c>
-      <c r="U10" t="s">
-        <v>181</v>
-      </c>
-      <c r="W10" t="s">
-        <v>164</v>
-      </c>
-      <c r="X10" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11" spans="2:26">
-      <c r="B11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D11" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H11" t="s">
-        <v>186</v>
-      </c>
-      <c r="J11" t="s">
-        <v>317</v>
-      </c>
-      <c r="K11" t="s">
-        <v>401</v>
-      </c>
-      <c r="L11">
-        <v>2.5085261082937969</v>
-      </c>
-      <c r="M11">
-        <v>0.38442213854971968</v>
-      </c>
-      <c r="O11" t="s">
-        <v>182</v>
-      </c>
-      <c r="P11" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>444</v>
-      </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>21</v>
-      </c>
-      <c r="T11" t="s">
-        <v>185</v>
-      </c>
-      <c r="U11" t="s">
-        <v>186</v>
-      </c>
-      <c r="W11" t="s">
-        <v>443</v>
-      </c>
-      <c r="X11" t="s">
-        <v>483</v>
-      </c>
-      <c r="Y11">
-        <v>22.356000000000002</v>
-      </c>
-      <c r="Z11">
-        <v>0.54621145523239889</v>
-      </c>
-    </row>
-    <row r="12" spans="2:26">
-      <c r="B12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" t="s">
-        <v>319</v>
-      </c>
-      <c r="D12" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" t="s">
-        <v>186</v>
-      </c>
-      <c r="J12" t="s">
-        <v>319</v>
-      </c>
-      <c r="K12" t="s">
-        <v>402</v>
-      </c>
-      <c r="L12">
-        <v>14.151077972051745</v>
-      </c>
-      <c r="M12">
-        <v>0.20452510677251201</v>
-      </c>
-      <c r="O12" t="s">
-        <v>182</v>
-      </c>
-      <c r="P12" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>446</v>
-      </c>
-      <c r="R12" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" t="s">
-        <v>21</v>
-      </c>
-      <c r="T12" t="s">
-        <v>185</v>
-      </c>
-      <c r="U12" t="s">
-        <v>186</v>
-      </c>
-      <c r="W12" t="s">
-        <v>445</v>
-      </c>
-      <c r="X12" t="s">
-        <v>484</v>
-      </c>
-      <c r="Y12">
-        <v>71.144999999999996</v>
-      </c>
-      <c r="Z12">
-        <v>0.51608117349821281</v>
-      </c>
-    </row>
-    <row r="13" spans="2:26">
-      <c r="B13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" t="s">
-        <v>322</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" t="s">
-        <v>186</v>
-      </c>
-      <c r="J13" t="s">
-        <v>321</v>
-      </c>
-      <c r="K13" t="s">
-        <v>403</v>
-      </c>
-      <c r="L13">
-        <v>11.382015059470456</v>
-      </c>
-      <c r="M13">
-        <v>0.2315323350735714</v>
-      </c>
-      <c r="O13" t="s">
-        <v>182</v>
-      </c>
-      <c r="P13" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>448</v>
-      </c>
-      <c r="R13" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" t="s">
-        <v>21</v>
-      </c>
-      <c r="T13" t="s">
-        <v>185</v>
-      </c>
-      <c r="U13" t="s">
-        <v>186</v>
-      </c>
-      <c r="W13" t="s">
-        <v>447</v>
-      </c>
-      <c r="X13" t="s">
-        <v>485</v>
-      </c>
-      <c r="Y13">
-        <v>20.269500000000001</v>
-      </c>
-      <c r="Z13">
-        <v>0.3762889566749637</v>
-      </c>
-    </row>
-    <row r="14" spans="2:26">
-      <c r="B14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" t="s">
-        <v>323</v>
-      </c>
-      <c r="D14" t="s">
-        <v>324</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H14" t="s">
-        <v>186</v>
-      </c>
-      <c r="J14" t="s">
-        <v>323</v>
-      </c>
-      <c r="K14" t="s">
-        <v>404</v>
-      </c>
-      <c r="L14">
-        <v>16.90477875687813</v>
-      </c>
-      <c r="M14">
-        <v>0.20403080837922249</v>
-      </c>
-      <c r="O14" t="s">
-        <v>182</v>
-      </c>
-      <c r="P14" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>450</v>
-      </c>
-      <c r="R14" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U14" t="s">
-        <v>186</v>
-      </c>
-      <c r="W14" t="s">
-        <v>449</v>
-      </c>
-      <c r="X14" t="s">
-        <v>486</v>
-      </c>
-      <c r="Y14">
-        <v>91.751999999999995</v>
-      </c>
-      <c r="Z14">
-        <v>0.52990963262679169</v>
-      </c>
-    </row>
-    <row r="15" spans="2:26">
-      <c r="B15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" t="s">
-        <v>325</v>
-      </c>
-      <c r="D15" t="s">
-        <v>326</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>185</v>
-      </c>
-      <c r="H15" t="s">
-        <v>186</v>
-      </c>
-      <c r="J15" t="s">
-        <v>325</v>
-      </c>
-      <c r="K15" t="s">
-        <v>405</v>
-      </c>
-      <c r="L15">
-        <v>18.676901648902387</v>
-      </c>
-      <c r="M15">
-        <v>0.1448045738501898</v>
-      </c>
-      <c r="O15" t="s">
-        <v>182</v>
-      </c>
-      <c r="P15" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>452</v>
-      </c>
-      <c r="R15" t="s">
-        <v>10</v>
-      </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>185</v>
-      </c>
-      <c r="U15" t="s">
-        <v>186</v>
-      </c>
-      <c r="W15" t="s">
-        <v>451</v>
-      </c>
-      <c r="X15" t="s">
-        <v>487</v>
-      </c>
-      <c r="Y15">
-        <v>9.2227499999999996</v>
-      </c>
-      <c r="Z15">
-        <v>0.37281254683293108</v>
-      </c>
-    </row>
-    <row r="16" spans="2:26">
-      <c r="B16" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" t="s">
-        <v>327</v>
-      </c>
-      <c r="D16" t="s">
-        <v>328</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>185</v>
-      </c>
-      <c r="H16" t="s">
-        <v>186</v>
-      </c>
-      <c r="J16" t="s">
-        <v>327</v>
-      </c>
-      <c r="K16" t="s">
-        <v>406</v>
-      </c>
-      <c r="L16">
-        <v>19.890436206910678</v>
-      </c>
-      <c r="M16">
-        <v>0.15568567988759499</v>
-      </c>
-      <c r="O16" t="s">
-        <v>182</v>
-      </c>
-      <c r="P16" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>454</v>
-      </c>
-      <c r="R16" t="s">
-        <v>10</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>185</v>
-      </c>
-      <c r="U16" t="s">
-        <v>186</v>
-      </c>
-      <c r="W16" t="s">
-        <v>453</v>
-      </c>
-      <c r="X16" t="s">
-        <v>488</v>
-      </c>
-      <c r="Y16">
-        <v>66.892499999999998</v>
-      </c>
-      <c r="Z16">
-        <v>0.50083145791048822</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26">
-      <c r="B17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" t="s">
-        <v>329</v>
-      </c>
-      <c r="D17" t="s">
-        <v>330</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>185</v>
-      </c>
-      <c r="H17" t="s">
-        <v>186</v>
-      </c>
-      <c r="J17" t="s">
-        <v>329</v>
-      </c>
-      <c r="K17" t="s">
-        <v>407</v>
-      </c>
-      <c r="L17">
-        <v>41.625170147271362</v>
-      </c>
-      <c r="M17">
-        <v>0.2641821193468662</v>
-      </c>
-      <c r="O17" t="s">
-        <v>182</v>
-      </c>
-      <c r="P17" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>456</v>
-      </c>
-      <c r="R17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" t="s">
-        <v>185</v>
-      </c>
-      <c r="U17" t="s">
-        <v>186</v>
-      </c>
-      <c r="W17" t="s">
-        <v>455</v>
-      </c>
-      <c r="X17" t="s">
-        <v>489</v>
-      </c>
-      <c r="Y17">
-        <v>46.789499999999997</v>
-      </c>
-      <c r="Z17">
-        <v>0.43722749499599151</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26">
-      <c r="B18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" t="s">
-        <v>331</v>
-      </c>
-      <c r="D18" t="s">
-        <v>332</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>185</v>
-      </c>
-      <c r="H18" t="s">
-        <v>186</v>
-      </c>
-      <c r="J18" t="s">
-        <v>331</v>
-      </c>
-      <c r="K18" t="s">
-        <v>408</v>
-      </c>
-      <c r="L18">
-        <v>60.246276232111249</v>
-      </c>
-      <c r="M18">
-        <v>0.29796998234161798</v>
-      </c>
-      <c r="O18" t="s">
-        <v>182</v>
-      </c>
-      <c r="P18" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>458</v>
-      </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" t="s">
-        <v>185</v>
-      </c>
-      <c r="U18" t="s">
-        <v>186</v>
-      </c>
-      <c r="W18" t="s">
-        <v>457</v>
-      </c>
-      <c r="X18" t="s">
-        <v>490</v>
-      </c>
-      <c r="Y18">
-        <v>15.483750000000001</v>
-      </c>
-      <c r="Z18">
-        <v>0.26931513046515498</v>
-      </c>
-    </row>
-    <row r="19" spans="2:26">
-      <c r="B19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D19" t="s">
-        <v>334</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>185</v>
-      </c>
-      <c r="H19" t="s">
-        <v>186</v>
-      </c>
-      <c r="J19" t="s">
-        <v>333</v>
-      </c>
-      <c r="K19" t="s">
-        <v>409</v>
-      </c>
-      <c r="L19">
-        <v>2.8310936025572326</v>
-      </c>
-      <c r="M19">
-        <v>0.11880817254789069</v>
-      </c>
-      <c r="O19" t="s">
-        <v>182</v>
-      </c>
-      <c r="P19" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>460</v>
-      </c>
-      <c r="R19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" t="s">
-        <v>185</v>
-      </c>
-      <c r="U19" t="s">
-        <v>186</v>
-      </c>
-      <c r="W19" t="s">
-        <v>459</v>
-      </c>
-      <c r="X19" t="s">
-        <v>491</v>
-      </c>
-      <c r="Y19">
-        <v>69.197999999999993</v>
-      </c>
-      <c r="Z19">
-        <v>0.45139689289404111</v>
-      </c>
-    </row>
-    <row r="20" spans="2:26">
-      <c r="B20" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" t="s">
-        <v>335</v>
-      </c>
-      <c r="D20" t="s">
-        <v>336</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" t="s">
-        <v>186</v>
-      </c>
-      <c r="J20" t="s">
-        <v>335</v>
-      </c>
-      <c r="K20" t="s">
-        <v>410</v>
-      </c>
-      <c r="L20">
-        <v>9.8725175016467617</v>
-      </c>
-      <c r="M20">
-        <v>0.26308084673963789</v>
-      </c>
-      <c r="O20" t="s">
-        <v>182</v>
-      </c>
-      <c r="P20" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>462</v>
-      </c>
-      <c r="R20" t="s">
-        <v>10</v>
-      </c>
-      <c r="S20" t="s">
-        <v>21</v>
-      </c>
-      <c r="T20" t="s">
-        <v>185</v>
-      </c>
-      <c r="U20" t="s">
-        <v>186</v>
-      </c>
-      <c r="W20" t="s">
-        <v>461</v>
-      </c>
-      <c r="X20" t="s">
-        <v>492</v>
-      </c>
-      <c r="Y20">
-        <v>7.6185</v>
-      </c>
-      <c r="Z20">
-        <v>0.3673526052541094</v>
-      </c>
-    </row>
-    <row r="21" spans="2:26">
-      <c r="B21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" t="s">
-        <v>337</v>
-      </c>
-      <c r="D21" t="s">
-        <v>338</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" t="s">
-        <v>337</v>
-      </c>
-      <c r="K21" t="s">
-        <v>411</v>
-      </c>
-      <c r="L21">
-        <v>4.2130667944593929</v>
-      </c>
-      <c r="M21">
-        <v>0.32715797544608061</v>
-      </c>
-      <c r="O21" t="s">
-        <v>182</v>
-      </c>
-      <c r="P21" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>464</v>
-      </c>
-      <c r="R21" t="s">
-        <v>10</v>
-      </c>
-      <c r="S21" t="s">
-        <v>21</v>
-      </c>
-      <c r="T21" t="s">
-        <v>185</v>
-      </c>
-      <c r="U21" t="s">
-        <v>186</v>
-      </c>
-      <c r="W21" t="s">
-        <v>463</v>
-      </c>
-      <c r="X21" t="s">
-        <v>493</v>
-      </c>
-      <c r="Y21">
-        <v>38.655749999999998</v>
-      </c>
-      <c r="Z21">
-        <v>0.54519508896051261</v>
-      </c>
-    </row>
-    <row r="22" spans="2:26">
-      <c r="B22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C22" t="s">
-        <v>339</v>
-      </c>
-      <c r="D22" t="s">
-        <v>340</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22" t="s">
-        <v>186</v>
-      </c>
-      <c r="J22" t="s">
-        <v>339</v>
-      </c>
-      <c r="K22" t="s">
-        <v>412</v>
-      </c>
-      <c r="L22">
-        <v>2.1088679510249264</v>
-      </c>
-      <c r="M22">
-        <v>9.3570387474760999E-2</v>
-      </c>
-      <c r="O22" t="s">
-        <v>182</v>
-      </c>
-      <c r="P22" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>466</v>
-      </c>
-      <c r="R22" t="s">
-        <v>10</v>
-      </c>
-      <c r="S22" t="s">
-        <v>21</v>
-      </c>
-      <c r="T22" t="s">
-        <v>185</v>
-      </c>
-      <c r="U22" t="s">
-        <v>186</v>
-      </c>
-      <c r="W22" t="s">
-        <v>465</v>
-      </c>
-      <c r="X22" t="s">
-        <v>494</v>
-      </c>
-      <c r="Y22">
-        <v>36.704999999999998</v>
-      </c>
-      <c r="Z22">
-        <v>0.51263869178343313</v>
-      </c>
-    </row>
-    <row r="23" spans="2:26">
-      <c r="B23" t="s">
-        <v>182</v>
-      </c>
-      <c r="C23" t="s">
-        <v>341</v>
-      </c>
-      <c r="D23" t="s">
-        <v>342</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>185</v>
-      </c>
-      <c r="H23" t="s">
-        <v>186</v>
-      </c>
-      <c r="J23" t="s">
-        <v>341</v>
-      </c>
-      <c r="K23" t="s">
-        <v>413</v>
-      </c>
-      <c r="L23">
-        <v>1.242396749224558</v>
-      </c>
-      <c r="M23">
-        <v>8.5955872642622402E-2</v>
-      </c>
-      <c r="O23" t="s">
-        <v>182</v>
-      </c>
-      <c r="P23" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>468</v>
-      </c>
-      <c r="R23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S23" t="s">
-        <v>21</v>
-      </c>
-      <c r="T23" t="s">
-        <v>185</v>
-      </c>
-      <c r="U23" t="s">
-        <v>186</v>
-      </c>
-      <c r="W23" t="s">
-        <v>467</v>
-      </c>
-      <c r="X23" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y23">
-        <v>72.104249999999993</v>
-      </c>
-      <c r="Z23">
-        <v>0.51445152950381501</v>
-      </c>
-    </row>
-    <row r="24" spans="2:26">
-      <c r="B24" t="s">
-        <v>182</v>
-      </c>
-      <c r="C24" t="s">
-        <v>343</v>
-      </c>
-      <c r="D24" t="s">
-        <v>344</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>185</v>
-      </c>
-      <c r="H24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J24" t="s">
-        <v>343</v>
-      </c>
-      <c r="K24" t="s">
-        <v>414</v>
-      </c>
-      <c r="L24">
-        <v>2.2821221811848558</v>
-      </c>
-      <c r="M24">
-        <v>0.14789509056852229</v>
-      </c>
-      <c r="O24" t="s">
-        <v>182</v>
-      </c>
-      <c r="P24" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>470</v>
-      </c>
-      <c r="R24" t="s">
-        <v>10</v>
-      </c>
-      <c r="S24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T24" t="s">
-        <v>185</v>
-      </c>
-      <c r="U24" t="s">
-        <v>186</v>
-      </c>
-      <c r="W24" t="s">
-        <v>469</v>
-      </c>
-      <c r="X24" t="s">
-        <v>496</v>
-      </c>
-      <c r="Y24">
-        <v>12.29025</v>
-      </c>
-      <c r="Z24">
-        <v>0.41736483903193727</v>
-      </c>
-    </row>
-    <row r="25" spans="2:26">
-      <c r="B25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" t="s">
-        <v>345</v>
-      </c>
-      <c r="D25" t="s">
-        <v>346</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>185</v>
-      </c>
-      <c r="H25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" t="s">
-        <v>345</v>
-      </c>
-      <c r="K25" t="s">
-        <v>415</v>
-      </c>
-      <c r="L25">
-        <v>7.6187600542008829</v>
-      </c>
-      <c r="M25">
-        <v>0.1016094115504282</v>
-      </c>
-      <c r="O25" t="s">
-        <v>182</v>
-      </c>
-      <c r="P25" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>472</v>
-      </c>
-      <c r="R25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S25" t="s">
-        <v>21</v>
-      </c>
-      <c r="T25" t="s">
-        <v>185</v>
-      </c>
-      <c r="U25" t="s">
-        <v>186</v>
-      </c>
-      <c r="W25" t="s">
-        <v>471</v>
-      </c>
-      <c r="X25" t="s">
-        <v>497</v>
-      </c>
-      <c r="Y25">
-        <v>7.4317500000000001</v>
-      </c>
-      <c r="Z25">
-        <v>0.50389818070132053</v>
-      </c>
-    </row>
-    <row r="26" spans="2:26">
-      <c r="B26" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" t="s">
-        <v>347</v>
-      </c>
-      <c r="D26" t="s">
-        <v>348</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>185</v>
-      </c>
-      <c r="H26" t="s">
-        <v>186</v>
-      </c>
-      <c r="J26" t="s">
-        <v>347</v>
-      </c>
-      <c r="K26" t="s">
-        <v>416</v>
-      </c>
-      <c r="L26">
-        <v>11.156586435503245</v>
-      </c>
-      <c r="M26">
-        <v>0.1458988949348993</v>
-      </c>
-      <c r="O26" t="s">
-        <v>182</v>
-      </c>
-      <c r="P26" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>474</v>
-      </c>
-      <c r="R26" t="s">
-        <v>10</v>
-      </c>
-      <c r="S26" t="s">
-        <v>21</v>
-      </c>
-      <c r="T26" t="s">
-        <v>185</v>
-      </c>
-      <c r="U26" t="s">
-        <v>186</v>
-      </c>
-      <c r="W26" t="s">
-        <v>473</v>
-      </c>
-      <c r="X26" t="s">
-        <v>498</v>
-      </c>
-      <c r="Y26">
-        <v>21.263249999999999</v>
-      </c>
-      <c r="Z26">
-        <v>0.49047893511766888</v>
-      </c>
-    </row>
-    <row r="27" spans="2:26">
-      <c r="B27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" t="s">
-        <v>349</v>
-      </c>
-      <c r="D27" t="s">
-        <v>350</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>185</v>
-      </c>
-      <c r="H27" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" t="s">
-        <v>349</v>
-      </c>
-      <c r="K27" t="s">
-        <v>417</v>
-      </c>
-      <c r="L27">
-        <v>13.317870473911716</v>
-      </c>
-      <c r="M27">
-        <v>0.20062430489929889</v>
-      </c>
-      <c r="O27" t="s">
-        <v>182</v>
-      </c>
-      <c r="P27" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>476</v>
-      </c>
-      <c r="R27" t="s">
-        <v>10</v>
-      </c>
-      <c r="S27" t="s">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s">
-        <v>185</v>
-      </c>
-      <c r="U27" t="s">
-        <v>186</v>
-      </c>
-      <c r="W27" t="s">
-        <v>475</v>
-      </c>
-      <c r="X27" t="s">
-        <v>499</v>
-      </c>
-      <c r="Y27">
-        <v>6.2925000000000004</v>
-      </c>
-      <c r="Z27">
-        <v>0.36116730033911121</v>
-      </c>
-    </row>
-    <row r="28" spans="2:26">
-      <c r="B28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" t="s">
-        <v>351</v>
-      </c>
-      <c r="D28" t="s">
-        <v>352</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" t="s">
-        <v>186</v>
-      </c>
-      <c r="J28" t="s">
-        <v>351</v>
-      </c>
-      <c r="K28" t="s">
-        <v>418</v>
-      </c>
-      <c r="L28">
-        <v>2.8668572503780223</v>
-      </c>
-      <c r="M28">
-        <v>0.1319359371558482</v>
-      </c>
-      <c r="O28" t="s">
-        <v>182</v>
-      </c>
-      <c r="P28" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>478</v>
-      </c>
-      <c r="R28" t="s">
-        <v>10</v>
-      </c>
-      <c r="S28" t="s">
-        <v>21</v>
-      </c>
-      <c r="T28" t="s">
-        <v>185</v>
-      </c>
-      <c r="U28" t="s">
-        <v>186</v>
-      </c>
-      <c r="W28" t="s">
-        <v>477</v>
-      </c>
-      <c r="X28" t="s">
-        <v>500</v>
-      </c>
-      <c r="Y28">
-        <v>8.7997499999999995</v>
-      </c>
-      <c r="Z28">
-        <v>0.37331655841332761</v>
-      </c>
-    </row>
-    <row r="29" spans="2:26">
-      <c r="B29" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" t="s">
-        <v>353</v>
-      </c>
-      <c r="D29" t="s">
-        <v>354</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>185</v>
-      </c>
-      <c r="H29" t="s">
-        <v>186</v>
-      </c>
-      <c r="J29" t="s">
-        <v>353</v>
-      </c>
-      <c r="K29" t="s">
-        <v>419</v>
-      </c>
-      <c r="L29">
-        <v>13.093923845373009</v>
-      </c>
-      <c r="M29">
-        <v>0.2266284858623237</v>
-      </c>
-      <c r="O29" t="s">
-        <v>182</v>
-      </c>
-      <c r="P29" t="s">
-        <v>479</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>480</v>
-      </c>
-      <c r="R29" t="s">
-        <v>10</v>
-      </c>
-      <c r="S29" t="s">
-        <v>21</v>
-      </c>
-      <c r="T29" t="s">
-        <v>185</v>
-      </c>
-      <c r="U29" t="s">
-        <v>186</v>
-      </c>
-      <c r="W29" t="s">
-        <v>479</v>
-      </c>
-      <c r="X29" t="s">
-        <v>501</v>
-      </c>
-      <c r="Y29">
-        <v>16.734749999999998</v>
-      </c>
-      <c r="Z29">
-        <v>0.42736446278598761</v>
-      </c>
-    </row>
-    <row r="30" spans="2:26">
-      <c r="B30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" t="s">
-        <v>355</v>
-      </c>
-      <c r="D30" t="s">
-        <v>356</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" t="s">
-        <v>186</v>
-      </c>
-      <c r="J30" t="s">
-        <v>355</v>
-      </c>
-      <c r="K30" t="s">
-        <v>420</v>
-      </c>
-      <c r="L30">
-        <v>6.0746622584304504</v>
-      </c>
-      <c r="M30">
-        <v>0.17149549523455249</v>
-      </c>
-      <c r="O30" t="s">
-        <v>182</v>
-      </c>
-      <c r="P30" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>482</v>
-      </c>
-      <c r="R30" t="s">
-        <v>10</v>
-      </c>
-      <c r="S30" t="s">
-        <v>21</v>
-      </c>
-      <c r="T30" t="s">
-        <v>185</v>
-      </c>
-      <c r="U30" t="s">
-        <v>186</v>
-      </c>
-      <c r="W30" t="s">
-        <v>481</v>
-      </c>
-      <c r="X30" t="s">
-        <v>502</v>
-      </c>
-      <c r="Y30">
-        <v>17.040749999999999</v>
-      </c>
-      <c r="Z30">
-        <v>0.4575194115073134</v>
-      </c>
-    </row>
-    <row r="31" spans="2:26">
-      <c r="B31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" t="s">
-        <v>357</v>
-      </c>
-      <c r="D31" t="s">
-        <v>358</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31" t="s">
-        <v>186</v>
-      </c>
-      <c r="J31" t="s">
-        <v>357</v>
-      </c>
-      <c r="K31" t="s">
-        <v>421</v>
-      </c>
-      <c r="L31">
-        <v>16.31886018972364</v>
-      </c>
-      <c r="M31">
-        <v>0.2166175963211332</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26">
-      <c r="B32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" t="s">
-        <v>359</v>
-      </c>
-      <c r="D32" t="s">
-        <v>360</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>185</v>
-      </c>
-      <c r="H32" t="s">
-        <v>186</v>
-      </c>
-      <c r="J32" t="s">
-        <v>359</v>
-      </c>
-      <c r="K32" t="s">
-        <v>422</v>
-      </c>
-      <c r="L32">
-        <v>11.364861678100382</v>
-      </c>
-      <c r="M32">
-        <v>0.2050393536459105</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
-      <c r="B33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C33" t="s">
-        <v>361</v>
-      </c>
-      <c r="D33" t="s">
-        <v>362</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" t="s">
-        <v>186</v>
-      </c>
-      <c r="J33" t="s">
-        <v>361</v>
-      </c>
-      <c r="K33" t="s">
-        <v>423</v>
-      </c>
-      <c r="L33">
-        <v>2.101579094416326</v>
-      </c>
-      <c r="M33">
-        <v>0.10530443211836429</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13">
-      <c r="B34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34" t="s">
-        <v>363</v>
-      </c>
-      <c r="D34" t="s">
-        <v>364</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" t="s">
-        <v>185</v>
-      </c>
-      <c r="H34" t="s">
-        <v>186</v>
-      </c>
-      <c r="J34" t="s">
-        <v>363</v>
-      </c>
-      <c r="K34" t="s">
-        <v>424</v>
-      </c>
-      <c r="L34">
-        <v>1.1455000262712256</v>
-      </c>
-      <c r="M34">
-        <v>0.10417096817583441</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13">
-      <c r="B35" t="s">
-        <v>182</v>
-      </c>
-      <c r="C35" t="s">
-        <v>365</v>
-      </c>
-      <c r="D35" t="s">
-        <v>366</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" t="s">
-        <v>185</v>
-      </c>
-      <c r="H35" t="s">
-        <v>186</v>
-      </c>
-      <c r="J35" t="s">
-        <v>365</v>
-      </c>
-      <c r="K35" t="s">
-        <v>425</v>
-      </c>
-      <c r="L35">
-        <v>1.4477313343828631</v>
-      </c>
-      <c r="M35">
-        <v>0.1444927629649353</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13">
-      <c r="B36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" t="s">
-        <v>367</v>
-      </c>
-      <c r="D36" t="s">
-        <v>368</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" t="s">
-        <v>185</v>
-      </c>
-      <c r="H36" t="s">
-        <v>186</v>
-      </c>
-      <c r="J36" t="s">
-        <v>367</v>
-      </c>
-      <c r="K36" t="s">
-        <v>426</v>
-      </c>
-      <c r="L36">
-        <v>7.8135900005455872</v>
-      </c>
-      <c r="M36">
-        <v>0.21608568854715859</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13">
-      <c r="B37" t="s">
-        <v>182</v>
-      </c>
-      <c r="C37" t="s">
-        <v>369</v>
-      </c>
-      <c r="D37" t="s">
-        <v>370</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" t="s">
-        <v>185</v>
-      </c>
-      <c r="H37" t="s">
-        <v>186</v>
-      </c>
-      <c r="J37" t="s">
-        <v>369</v>
-      </c>
-      <c r="K37" t="s">
-        <v>427</v>
-      </c>
-      <c r="L37">
-        <v>9.7399044969678972</v>
-      </c>
-      <c r="M37">
-        <v>0.22472775896605149</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13">
-      <c r="B38" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38" t="s">
-        <v>371</v>
-      </c>
-      <c r="D38" t="s">
-        <v>372</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" t="s">
-        <v>185</v>
-      </c>
-      <c r="H38" t="s">
-        <v>186</v>
-      </c>
-      <c r="J38" t="s">
-        <v>371</v>
-      </c>
-      <c r="K38" t="s">
-        <v>428</v>
-      </c>
-      <c r="L38">
-        <v>11.047069314867423</v>
-      </c>
-      <c r="M38">
-        <v>0.23523818012163661</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13">
-      <c r="B39" t="s">
-        <v>182</v>
-      </c>
-      <c r="C39" t="s">
-        <v>373</v>
-      </c>
-      <c r="D39" t="s">
-        <v>374</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" t="s">
-        <v>185</v>
-      </c>
-      <c r="H39" t="s">
-        <v>186</v>
-      </c>
-      <c r="J39" t="s">
-        <v>373</v>
-      </c>
-      <c r="K39" t="s">
-        <v>429</v>
-      </c>
-      <c r="L39">
-        <v>26.32580391715549</v>
-      </c>
-      <c r="M39">
-        <v>0.28020228387492641</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13">
-      <c r="B40" t="s">
-        <v>182</v>
-      </c>
-      <c r="C40" t="s">
-        <v>375</v>
-      </c>
-      <c r="D40" t="s">
-        <v>376</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40" t="s">
-        <v>185</v>
-      </c>
-      <c r="H40" t="s">
-        <v>186</v>
-      </c>
-      <c r="J40" t="s">
-        <v>375</v>
-      </c>
-      <c r="K40" t="s">
-        <v>430</v>
-      </c>
-      <c r="L40">
-        <v>13.093319261533304</v>
-      </c>
-      <c r="M40">
-        <v>0.23411117543992219</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13">
-      <c r="B41" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" t="s">
-        <v>377</v>
-      </c>
-      <c r="D41" t="s">
-        <v>378</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41" t="s">
-        <v>185</v>
-      </c>
-      <c r="H41" t="s">
-        <v>186</v>
-      </c>
-      <c r="J41" t="s">
-        <v>377</v>
-      </c>
-      <c r="K41" t="s">
-        <v>431</v>
-      </c>
-      <c r="L41">
-        <v>12.996823777257559</v>
-      </c>
-      <c r="M41">
-        <v>0.2721920265122556</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13">
-      <c r="B42" t="s">
-        <v>182</v>
-      </c>
-      <c r="C42" t="s">
-        <v>379</v>
-      </c>
-      <c r="D42" t="s">
-        <v>380</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42" t="s">
-        <v>185</v>
-      </c>
-      <c r="H42" t="s">
-        <v>186</v>
-      </c>
-      <c r="J42" t="s">
-        <v>379</v>
-      </c>
-      <c r="K42" t="s">
-        <v>432</v>
-      </c>
-      <c r="L42">
-        <v>29.723767601585116</v>
-      </c>
-      <c r="M42">
-        <v>0.298758552939206</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13">
-      <c r="B43" t="s">
-        <v>182</v>
-      </c>
-      <c r="C43" t="s">
-        <v>381</v>
-      </c>
-      <c r="D43" t="s">
-        <v>382</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43" t="s">
-        <v>185</v>
-      </c>
-      <c r="H43" t="s">
-        <v>186</v>
-      </c>
-      <c r="J43" t="s">
-        <v>381</v>
-      </c>
-      <c r="K43" t="s">
-        <v>433</v>
-      </c>
-      <c r="L43">
-        <v>23.718762539626265</v>
-      </c>
-      <c r="M43">
-        <v>0.3459103784669153</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13">
-      <c r="B44" t="s">
-        <v>182</v>
-      </c>
-      <c r="C44" t="s">
-        <v>383</v>
-      </c>
-      <c r="D44" t="s">
-        <v>384</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44" t="s">
-        <v>185</v>
-      </c>
-      <c r="H44" t="s">
-        <v>186</v>
-      </c>
-      <c r="J44" t="s">
-        <v>383</v>
-      </c>
-      <c r="K44" t="s">
-        <v>434</v>
-      </c>
-      <c r="L44">
-        <v>27.436549011428941</v>
-      </c>
-      <c r="M44">
-        <v>0.29648623812476937</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13">
-      <c r="B45" t="s">
-        <v>182</v>
-      </c>
-      <c r="C45" t="s">
-        <v>385</v>
-      </c>
-      <c r="D45" t="s">
-        <v>386</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45" t="s">
-        <v>185</v>
-      </c>
-      <c r="H45" t="s">
-        <v>186</v>
-      </c>
-      <c r="J45" t="s">
-        <v>385</v>
-      </c>
-      <c r="K45" t="s">
-        <v>435</v>
-      </c>
-      <c r="L45">
-        <v>9.8243028619644921</v>
-      </c>
-      <c r="M45">
-        <v>0.39497357495459801</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13">
-      <c r="B46" t="s">
-        <v>182</v>
-      </c>
-      <c r="C46" t="s">
-        <v>387</v>
-      </c>
-      <c r="D46" t="s">
-        <v>388</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" t="s">
-        <v>185</v>
-      </c>
-      <c r="H46" t="s">
-        <v>186</v>
-      </c>
-      <c r="J46" t="s">
-        <v>387</v>
-      </c>
-      <c r="K46" t="s">
-        <v>436</v>
-      </c>
-      <c r="L46">
-        <v>39.894345732245682</v>
-      </c>
-      <c r="M46">
-        <v>0.31484184238651358</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13">
-      <c r="B47" t="s">
-        <v>182</v>
-      </c>
-      <c r="C47" t="s">
-        <v>389</v>
-      </c>
-      <c r="D47" t="s">
-        <v>390</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>21</v>
-      </c>
-      <c r="G47" t="s">
-        <v>185</v>
-      </c>
-      <c r="H47" t="s">
-        <v>186</v>
-      </c>
-      <c r="J47" t="s">
-        <v>389</v>
-      </c>
-      <c r="K47" t="s">
-        <v>437</v>
-      </c>
-      <c r="L47">
-        <v>18.730841731080265</v>
-      </c>
-      <c r="M47">
-        <v>0.21521638484570091</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13">
-      <c r="B48" t="s">
-        <v>182</v>
-      </c>
-      <c r="C48" t="s">
-        <v>391</v>
-      </c>
-      <c r="D48" t="s">
-        <v>392</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>21</v>
-      </c>
-      <c r="G48" t="s">
-        <v>185</v>
-      </c>
-      <c r="H48" t="s">
-        <v>186</v>
-      </c>
-      <c r="J48" t="s">
-        <v>391</v>
-      </c>
-      <c r="K48" t="s">
-        <v>438</v>
-      </c>
-      <c r="L48">
-        <v>20.256717029567771</v>
-      </c>
-      <c r="M48">
-        <v>0.18932181859163921</v>
-      </c>
-    </row>
-    <row r="49" spans="2:13">
-      <c r="B49" t="s">
-        <v>182</v>
-      </c>
-      <c r="C49" t="s">
-        <v>393</v>
-      </c>
-      <c r="D49" t="s">
-        <v>394</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" t="s">
-        <v>185</v>
-      </c>
-      <c r="H49" t="s">
-        <v>186</v>
-      </c>
-      <c r="J49" t="s">
-        <v>393</v>
-      </c>
-      <c r="K49" t="s">
-        <v>439</v>
-      </c>
-      <c r="L49">
-        <v>63.11239557797159</v>
-      </c>
-      <c r="M49">
-        <v>0.40984504679108119</v>
-      </c>
-    </row>
-    <row r="50" spans="2:13">
-      <c r="B50" t="s">
-        <v>182</v>
-      </c>
-      <c r="C50" t="s">
-        <v>395</v>
-      </c>
-      <c r="D50" t="s">
-        <v>396</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50" t="s">
-        <v>185</v>
-      </c>
-      <c r="H50" t="s">
-        <v>186</v>
-      </c>
-      <c r="J50" t="s">
-        <v>395</v>
-      </c>
-      <c r="K50" t="s">
-        <v>440</v>
-      </c>
-      <c r="L50">
-        <v>38.222782480143309</v>
-      </c>
-      <c r="M50">
-        <v>0.33995720411689029</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13">
-      <c r="B51" t="s">
-        <v>182</v>
-      </c>
-      <c r="C51" t="s">
-        <v>397</v>
-      </c>
-      <c r="D51" t="s">
-        <v>398</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" t="s">
-        <v>185</v>
-      </c>
-      <c r="H51" t="s">
-        <v>186</v>
-      </c>
-      <c r="J51" t="s">
-        <v>397</v>
-      </c>
-      <c r="K51" t="s">
-        <v>441</v>
-      </c>
-      <c r="L51">
-        <v>41.926633570495007</v>
-      </c>
-      <c r="M51">
-        <v>0.33623081374544261</v>
-      </c>
-    </row>
-    <row r="52" spans="2:13">
-      <c r="B52" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52" t="s">
-        <v>399</v>
-      </c>
-      <c r="D52" t="s">
-        <v>400</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52" t="s">
-        <v>185</v>
-      </c>
-      <c r="H52" t="s">
-        <v>186</v>
-      </c>
-      <c r="J52" t="s">
-        <v>399</v>
-      </c>
-      <c r="K52" t="s">
-        <v>442</v>
-      </c>
-      <c r="L52">
-        <v>47.281374191365337</v>
-      </c>
-      <c r="M52">
-        <v>0.31961940066535188</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396183E4-8EF7-4A86-A94A-EC4A134110FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5198020-BA7F-41C3-87F6-3FEA4C4DF158}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -10388,30 +10233,30 @@
         <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="K10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M10" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="N10" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="O10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -10432,10 +10277,10 @@
         <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -10444,15 +10289,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P11" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -10470,13 +10315,13 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="J12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -10485,15 +10330,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P12" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -10511,13 +10356,13 @@
         <v>4400</v>
       </c>
       <c r="H13" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="J13" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -10526,15 +10371,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P13" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -10552,13 +10397,13 @@
         <v>155</v>
       </c>
       <c r="H14" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="J14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -10567,15 +10412,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P14" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -10593,13 +10438,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="J15" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -10608,15 +10453,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P15" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -10637,10 +10482,10 @@
         <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -10649,15 +10494,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P16" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -10675,14 +10520,14 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="s">
+        <v>496</v>
+      </c>
+      <c r="J17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K17" t="s">
         <v>505</v>
       </c>
-      <c r="J17" t="s">
-        <v>182</v>
-      </c>
-      <c r="K17" t="s">
-        <v>514</v>
-      </c>
       <c r="M17" t="s">
         <v>10</v>
       </c>
@@ -10690,15 +10535,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P17" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -10716,14 +10561,14 @@
         <v>2050</v>
       </c>
       <c r="H18" t="s">
+        <v>497</v>
+      </c>
+      <c r="J18" t="s">
+        <v>172</v>
+      </c>
+      <c r="K18" t="s">
         <v>506</v>
       </c>
-      <c r="J18" t="s">
-        <v>182</v>
-      </c>
-      <c r="K18" t="s">
-        <v>515</v>
-      </c>
       <c r="M18" t="s">
         <v>10</v>
       </c>
@@ -10731,15 +10576,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P18" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -10757,14 +10602,14 @@
         <v>70</v>
       </c>
       <c r="H19" t="s">
+        <v>498</v>
+      </c>
+      <c r="J19" t="s">
+        <v>172</v>
+      </c>
+      <c r="K19" t="s">
         <v>507</v>
       </c>
-      <c r="J19" t="s">
-        <v>182</v>
-      </c>
-      <c r="K19" t="s">
-        <v>516</v>
-      </c>
       <c r="M19" t="s">
         <v>10</v>
       </c>
@@ -10772,15 +10617,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P19" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -10798,30 +10643,30 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
+        <v>499</v>
+      </c>
+      <c r="J20" t="s">
+        <v>172</v>
+      </c>
+      <c r="K20" t="s">
         <v>508</v>
       </c>
-      <c r="J20" t="s">
-        <v>182</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
         <v>517</v>
       </c>
-      <c r="M20" t="s">
-        <v>10</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
-        <v>526</v>
-      </c>
       <c r="P20" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -10842,27 +10687,27 @@
         <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
+        <v>509</v>
+      </c>
+      <c r="M21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>517</v>
+      </c>
+      <c r="P21" t="s">
         <v>518</v>
-      </c>
-      <c r="M21" t="s">
-        <v>10</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>526</v>
-      </c>
-      <c r="P21" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -10880,13 +10725,13 @@
         <v>700</v>
       </c>
       <c r="H22" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="J22" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -10895,15 +10740,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P22" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -10921,13 +10766,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="J23" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -10936,15 +10781,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P23" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -10965,10 +10810,10 @@
         <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -10977,15 +10822,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P24" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -11003,13 +10848,13 @@
         <v>1850</v>
       </c>
       <c r="H25" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="J25" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -11018,15 +10863,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P25" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -11044,13 +10889,13 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="J26" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -11059,15 +10904,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P26" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -11088,10 +10933,10 @@
         <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -11100,15 +10945,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="P27" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -11126,12 +10971,12 @@
         <v>3550</v>
       </c>
       <c r="H28" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -11149,12 +10994,12 @@
         <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -11177,7 +11022,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -11195,12 +11040,12 @@
         <v>400</v>
       </c>
       <c r="H31" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -11218,12 +11063,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -11246,7 +11091,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -11264,12 +11109,12 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -11287,12 +11132,12 @@
         <v>2100</v>
       </c>
       <c r="H35" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -11310,12 +11155,12 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -11333,12 +11178,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -11361,7 +11206,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -11379,12 +11224,12 @@
         <v>2100</v>
       </c>
       <c r="H39" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -11402,12 +11247,12 @@
         <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -11430,7 +11275,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -11448,12 +11293,12 @@
         <v>4200</v>
       </c>
       <c r="H42" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -11471,12 +11316,12 @@
         <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -11499,7 +11344,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -11517,12 +11362,12 @@
         <v>4000</v>
       </c>
       <c r="H45" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -11540,12 +11385,12 @@
         <v>170</v>
       </c>
       <c r="H46" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -11568,7 +11413,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -11586,12 +11431,12 @@
         <v>4300</v>
       </c>
       <c r="H48" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -11609,12 +11454,12 @@
         <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -11637,7 +11482,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -11655,12 +11500,12 @@
         <v>0.23</v>
       </c>
       <c r="H51" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -11678,12 +11523,12 @@
         <v>550</v>
       </c>
       <c r="H52" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -11701,12 +11546,12 @@
         <v>18</v>
       </c>
       <c r="H53" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -11724,12 +11569,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -11752,7 +11597,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -11770,12 +11615,12 @@
         <v>1300</v>
       </c>
       <c r="H56" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -11793,12 +11638,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -11821,7 +11666,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -11839,12 +11684,12 @@
         <v>1600</v>
       </c>
       <c r="H59" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -11862,12 +11707,12 @@
         <v>55</v>
       </c>
       <c r="H60" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -11890,7 +11735,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -11908,12 +11753,12 @@
         <v>1900</v>
       </c>
       <c r="H62" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -11931,15 +11776,15 @@
         <v>70</v>
       </c>
       <c r="H63" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -11959,10 +11804,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C65" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -11977,15 +11822,15 @@
         <v>0.43</v>
       </c>
       <c r="H65" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C66" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -12000,15 +11845,15 @@
         <v>2200</v>
       </c>
       <c r="H66" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C67" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -12023,15 +11868,15 @@
         <v>65</v>
       </c>
       <c r="H67" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C68" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -12046,15 +11891,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="C69" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -12074,10 +11919,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="C70" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -12092,15 +11937,15 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H70" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="C71" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -12115,15 +11960,15 @@
         <v>1470</v>
       </c>
       <c r="H71" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="C72" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -12138,15 +11983,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="C73" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -12161,7 +12006,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
